--- a/src/attributions/attributions_saliency_traj_79.xlsx
+++ b/src/attributions/attributions_saliency_traj_79.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3058689832687378</v>
+        <v>5.973326187813655e-05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05003009736537933</v>
+        <v>1.285238795389887e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02761637419462204</v>
+        <v>3.037781061721034e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2373151183128357</v>
+        <v>1.441802760382416e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1947989463806152</v>
+        <v>1.311175583396107e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3379333317279816</v>
+        <v>1.246393003384583e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2231224179267883</v>
+        <v>5.768785058535286e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2124256938695908</v>
+        <v>3.218299070795183e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4086758494377136</v>
+        <v>4.928704129270045e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3815065622329712</v>
+        <v>6.224016397027299e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1620949357748032</v>
+        <v>8.197151146305259e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05838365107774734</v>
+        <v>2.145635880879126e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2079458087682724</v>
+        <v>1.698647793091368e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2082099616527557</v>
+        <v>4.265358802513219e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1976491659879684</v>
+        <v>5.730317752750125e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2556715607643127</v>
+        <v>4.132664344069781e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05253306776285172</v>
+        <v>8.218057701014914e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5473004579544067</v>
+        <v>3.964725692640059e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004552721977233887</v>
+        <v>2.124296315741958e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0684790164232254</v>
+        <v>1.066370077751344e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02317411452531815</v>
+        <v>2.721897089941194e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1888930350542068</v>
+        <v>6.976789336476941e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.07427936792373657</v>
+        <v>6.89692660671426e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>0.171366885304451</v>
+        <v>5.747176146542188e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2290947288274765</v>
+        <v>4.174255536781857e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.09931328892707825</v>
+        <v>5.6361454880971e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08312685042619705</v>
+        <v>2.441295464450377e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0341656357049942</v>
+        <v>1.303789667872479e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.09604257345199585</v>
+        <v>1.837337777033099e-06</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.006259713787585497</v>
+        <v>4.038213319290662e-06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1595853120088577</v>
+        <v>9.326752660854254e-06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1270586848258972</v>
+        <v>6.091515388106927e-06</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0354803055524826</v>
+        <v>2.858738480426837e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2163585722446442</v>
+        <v>8.917304512578994e-07</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1513155698776245</v>
+        <v>3.710760893227416e-06</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.3058339059352875</v>
+        <v>3.854157966998173e-06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1371037214994431</v>
+        <v>6.562665021192515e-06</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1201025992631912</v>
+        <v>9.587685781298205e-06</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01689157448709011</v>
+        <v>1.530617191747297e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.2546190023422241</v>
+        <v>8.561457434552722e-06</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0258258692920208</v>
+        <v>1.092671482183505e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.060645941644907</v>
+        <v>1.577411694597686e-07</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.08838438242673874</v>
+        <v>1.980397200895823e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.08131232857704163</v>
+        <v>1.646474970584677e-06</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.2164815664291382</v>
+        <v>2.31311628340336e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.3292589783668518</v>
+        <v>2.265966577397194e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.04012253507971764</v>
+        <v>1.153377525042742e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.09635854512453079</v>
+        <v>7.264880878210533e-06</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.01419409364461899</v>
+        <v>1.752110802044626e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.6453368663787842</v>
+        <v>2.838223736034706e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.07927184551954269</v>
+        <v>7.794717021170072e-06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2412108480930328</v>
+        <v>1.843902168729983e-06</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.4250987470149994</v>
+        <v>6.192633463797392e-07</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1564589738845825</v>
+        <v>1.715330313345476e-06</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.09120140969753265</v>
+        <v>1.279921525565442e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.07401041686534882</v>
+        <v>5.99204304307932e-06</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.08683926612138748</v>
+        <v>1.496874756412581e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1942230612039566</v>
+        <v>9.426321412320249e-06</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1926861256361008</v>
+        <v>1.133298701461172e-05</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1659304350614548</v>
+        <v>4.891813205176732e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1769639551639557</v>
+        <v>6.089329644964891e-07</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1400406658649445</v>
+        <v>1.848628926381934e-06</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.3731884658336639</v>
+        <v>8.967673238657881e-06</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1164070591330528</v>
+        <v>2.085964479192626e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1082636341452599</v>
+        <v>3.645292736109695e-06</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.04740098118782043</v>
+        <v>2.028045173574355e-06</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1375365555286407</v>
+        <v>4.097887995158089e-06</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1623181104660034</v>
+        <v>1.035738023347221e-05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01986055821180344</v>
+        <v>3.11149551635026e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.2306993901729584</v>
+        <v>5.970267920929473e-06</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.05261211842298508</v>
+        <v>8.896317922335584e-07</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.07959209382534027</v>
+        <v>2.641327682795236e-06</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.2117832899093628</v>
+        <v>1.935791806317866e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.02559088543057442</v>
+        <v>7.442351943609538e-06</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.07659400999546051</v>
+        <v>1.526793130324222e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.07246696949005127</v>
+        <v>1.086874726752285e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.03277121111750603</v>
+        <v>1.087541932065506e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.06607988476753235</v>
+        <v>7.095442242643912e-07</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1536944806575775</v>
+        <v>4.961655122315278e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.02554604224860668</v>
+        <v>2.317969347132021e-06</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0838070884346962</v>
+        <v>4.011754754174035e-06</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.04331976547837257</v>
+        <v>1.27444172903779e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.08724860101938248</v>
+        <v>6.556006724167673e-07</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.001438716426491737</v>
+        <v>4.491075742407702e-06</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.04346483573317528</v>
+        <v>5.74519708607113e-06</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.03880320861935616</v>
+        <v>4.33442301073228e-06</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01230340171605349</v>
+        <v>7.632075380570313e-07</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.03123391047120094</v>
+        <v>2.711431079660542e-08</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.07280706614255905</v>
+        <v>1.133350906457053e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.01643028855323792</v>
+        <v>1.846083591772185e-06</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.01224157214164734</v>
+        <v>2.945348796856706e-06</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.008791076019406319</v>
+        <v>6.401531209121458e-06</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.04050825163722038</v>
+        <v>9.842949111771304e-06</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.08346030116081238</v>
+        <v>5.585557119047735e-06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1163903176784515</v>
+        <v>1.777282523107715e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1737464368343353</v>
+        <v>2.124837919836864e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1206794753670692</v>
+        <v>3.955137799493968e-06</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0989825576543808</v>
+        <v>1.480871674175432e-06</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.07172499597072601</v>
+        <v>7.376397661573719e-06</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.03186648339033127</v>
+        <v>1.236739080923144e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.09611416608095169</v>
+        <v>3.275734798080521e-06</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.01327014900743961</v>
+        <v>8.047480150707997e-06</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.04828255251049995</v>
+        <v>5.137025254953187e-06</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.06244945526123047</v>
+        <v>2.66792562797491e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.007351364940404892</v>
+        <v>2.058204700006172e-06</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.02300369739532471</v>
+        <v>9.816262718231883e-07</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.09634909778833389</v>
+        <v>4.149152346144547e-07</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.005781402811408043</v>
+        <v>7.407262501146761e-07</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.02910564839839935</v>
+        <v>1.70809325936716e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2005546689033508</v>
+        <v>5.318489274941385e-05</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.06109610572457314</v>
+        <v>1.22121391541441e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1724587231874466</v>
+        <v>1.701495421002619e-05</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.4782906174659729</v>
+        <v>6.897940693306737e-06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.4422880709171295</v>
+        <v>1.45622007039492e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.006954226642847061</v>
+        <v>6.602851044590352e-06</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1332303434610367</v>
+        <v>4.787771104020067e-06</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2914436459541321</v>
+        <v>8.478783456666861e-06</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.07229285687208176</v>
+        <v>1.042804706230527e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.07734482735395432</v>
+        <v>4.18718445871491e-06</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.04840406030416489</v>
+        <v>1.219304158439627e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1698618829250336</v>
+        <v>6.221323019417468e-06</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.442369282245636</v>
+        <v>1.632263774808962e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1344652026891708</v>
+        <v>1.400369683324243e-06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.02949535101652145</v>
+        <v>2.516298081900459e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.3574561774730682</v>
+        <v>4.933292075293139e-06</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.00031253881752491</v>
+        <v>3.539652880135691e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.002415938302874565</v>
+        <v>6.475143891293555e-06</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2221521884202957</v>
+        <v>4.470784460863797e-06</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.04442064091563225</v>
+        <v>2.546043469919823e-05</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.1084783524274826</v>
+        <v>7.454285878338851e-06</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.01618286967277527</v>
+        <v>1.291676198889036e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.05646276473999023</v>
+        <v>2.396393938397523e-06</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.02757369726896286</v>
+        <v>1.948122417161358e-06</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0112281758338213</v>
+        <v>6.022510206094012e-06</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1083380579948425</v>
+        <v>5.683461949956836e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.02579103037714958</v>
+        <v>1.594760033185594e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.04734017327427864</v>
+        <v>4.515548425843008e-06</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.02251674607396126</v>
+        <v>2.171294909203425e-06</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.00875704362988472</v>
+        <v>2.026212769123958e-06</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.1200782507658005</v>
+        <v>4.705517312686425e-06</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1196329072117805</v>
+        <v>5.86079181630339e-07</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.02104384452104568</v>
+        <v>2.575959115347359e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.02454358153045177</v>
+        <v>7.393076089101669e-07</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.03048543818295002</v>
+        <v>4.960156275046756e-06</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.06986147165298462</v>
+        <v>8.422085556958336e-06</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1954388469457626</v>
+        <v>4.762940534419613e-06</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.008856994099915028</v>
+        <v>4.61953277408611e-07</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.06757274270057678</v>
+        <v>8.78686932992423e-06</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.177154928445816</v>
+        <v>3.356689148859004e-07</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.1051875278353691</v>
+        <v>1.404037720931228e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.1236884370446205</v>
+        <v>7.5754537647299e-06</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.1126724630594254</v>
+        <v>5.836985565110808e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.07878687232732773</v>
+        <v>9.486335329711437e-06</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.05549491196870804</v>
+        <v>1.358401459583547e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.08264975994825363</v>
+        <v>6.099481652199756e-06</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.001120232045650482</v>
+        <v>8.211860404117033e-06</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.06751833111047745</v>
+        <v>6.037912953615887e-06</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03195677697658539</v>
+        <v>3.429820480960188e-07</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.001735758036375046</v>
+        <v>6.215578650881071e-06</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.03544500097632408</v>
+        <v>1.140125618803722e-06</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.149189218878746</v>
+        <v>2.714708216444706e-06</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.04426223784685135</v>
+        <v>1.445264729227347e-06</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.09770422428846359</v>
+        <v>3.135681254207157e-05</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.1494440138339996</v>
+        <v>7.149727935029659e-06</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.01742632128298283</v>
+        <v>1.731129032123135e-06</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1188423037528992</v>
+        <v>7.700451533310115e-06</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.132126584649086</v>
+        <v>4.461472144612344e-06</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1026455536484718</v>
+        <v>1.570807216921821e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.01316037401556969</v>
+        <v>5.326831342244986e-06</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2366559356451035</v>
+        <v>1.862173348854412e-07</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.08071444928646088</v>
+        <v>3.132128313154681e-06</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1169547215104103</v>
+        <v>7.358527909673285e-06</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.07350189238786697</v>
+        <v>1.208567118737847e-05</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.1137984395027161</v>
+        <v>2.636547651491128e-05</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.02660071104764938</v>
+        <v>1.918648740684148e-05</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1770925670862198</v>
+        <v>2.194421904277988e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.1938930153846741</v>
+        <v>1.146120553130459e-06</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.07893882691860199</v>
+        <v>1.077136766980402e-05</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.03413866087794304</v>
+        <v>1.088234603230376e-05</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.124619722366333</v>
+        <v>1.596140236870269e-06</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.02853546664118767</v>
+        <v>1.74408960447181e-05</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.02652196958661079</v>
+        <v>4.242780505592236e-06</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.01190339028835297</v>
+        <v>2.618961616462911e-06</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.009347282350063324</v>
+        <v>1.540893026685808e-05</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.04230314493179321</v>
+        <v>1.991195858863648e-05</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1067606955766678</v>
+        <v>6.255202606553212e-06</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.02045245096087456</v>
+        <v>7.27225597074721e-06</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.08968875557184219</v>
+        <v>9.090266757993959e-06</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.02400924265384674</v>
+        <v>6.752666195097845e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.005435765720903873</v>
+        <v>2.395356568740681e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03470630198717117</v>
+        <v>9.451431105844676e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000262263318290934</v>
+        <v>1.117304418585263e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01841084472835064</v>
+        <v>9.101351315621287e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004958399571478367</v>
+        <v>3.731412652996369e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00655114883556962</v>
+        <v>4.595406426233239e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005210380768403411</v>
+        <v>2.638697333168238e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003262638347223401</v>
+        <v>3.602658398449421e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009262301027774811</v>
+        <v>5.315792805049568e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007206320762634277</v>
+        <v>1.566737228131387e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02213429659605026</v>
+        <v>0.0001078167333616875</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00177839130628854</v>
+        <v>4.109549990971573e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01623950898647308</v>
+        <v>0.0001122994799516164</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01078859157860279</v>
+        <v>5.545944077312015e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01247734948992729</v>
+        <v>3.793601717916317e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001987557392567396</v>
+        <v>3.147452298435383e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.005643961485475302</v>
+        <v>9.243576641893014e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002803092822432518</v>
+        <v>4.638966856873594e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001233384682564065</v>
+        <v>1.683537902863463e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004503657110035419</v>
+        <v>7.812305739207659e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001234111725352705</v>
+        <v>1.145590204032487e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004433783702552319</v>
+        <v>4.368378370145365e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003854284877888858</v>
+        <v>1.21203129310743e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>9.732623584568501e-05</v>
+        <v>1.191913179354742e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006019000429660082</v>
+        <v>3.271585683251033e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001766265369951725</v>
+        <v>1.439499737898586e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002419288037344813</v>
+        <v>2.213366678915918e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002908200025558472</v>
+        <v>1.639849142520688e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005330296698957682</v>
+        <v>1.083991719497135e-06</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0005359944771043956</v>
+        <v>3.54014241565892e-06</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.00126742897555232</v>
+        <v>2.903117547248257e-06</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004192954394966364</v>
+        <v>1.592903390701395e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.002940087579190731</v>
+        <v>1.40876318255323e-05</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.114854916930199e-05</v>
+        <v>3.748422386706807e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.002801355673000216</v>
+        <v>2.402881591478945e-06</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.002101049991324544</v>
+        <v>1.331209091404162e-06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.002857648767530918</v>
+        <v>1.700304437690647e-06</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.003087757155299187</v>
+        <v>1.393858110532165e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>9.892668458633125e-05</v>
+        <v>1.192778108816128e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001691636629402637</v>
+        <v>1.266626986762276e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001943061593919992</v>
+        <v>9.98452196654398e-06</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.005357127636671066</v>
+        <v>1.488291582063539e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001154277706518769</v>
+        <v>1.08798012661282e-05</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.001881743664853275</v>
+        <v>4.409845132613555e-06</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.00182235729880631</v>
+        <v>1.911066192405997e-06</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.004057441838085651</v>
+        <v>4.225174052407965e-06</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.02354514971375465</v>
+        <v>5.768627306679264e-05</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002704796614125371</v>
+        <v>1.222236642206553e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00753382034599781</v>
+        <v>4.891767457593232e-05</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.006403997540473938</v>
+        <v>6.808282341808081e-05</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001457073609344661</v>
+        <v>1.42066992339096e-05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00351324793882668</v>
+        <v>3.679328983707819e-07</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.002105621621012688</v>
+        <v>1.117878127843142e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.00358275044709444</v>
+        <v>1.56909300130792e-06</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.003171365708112717</v>
+        <v>1.693400008662138e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.004336100071668625</v>
+        <v>2.718527866818476e-06</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.003935746382921934</v>
+        <v>1.319320472248364e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.001421477878466249</v>
+        <v>9.96615199255757e-08</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.009157677181065083</v>
+        <v>1.477705700381193e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.004048041999340057</v>
+        <v>2.05440774152521e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.003442454151809216</v>
+        <v>2.968567514471943e-06</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004593473393470049</v>
+        <v>3.517023287713528e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0005326810642145574</v>
+        <v>1.075673935702071e-06</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.004404628649353981</v>
+        <v>7.418742370646214e-06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0007431918056681752</v>
+        <v>1.132347188104177e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001898696413263679</v>
+        <v>3.671078957268037e-06</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.004180111922323704</v>
+        <v>1.572048859088682e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003526601940393448</v>
+        <v>1.860950214904733e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001014311332255602</v>
+        <v>2.051371893685427e-06</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0006969040259718895</v>
+        <v>6.807772479078267e-08</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0009264511754736304</v>
+        <v>6.245482836675365e-06</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0020134337246418</v>
+        <v>8.915991202229634e-06</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002065651118755341</v>
+        <v>8.913889359973837e-07</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01240516267716885</v>
+        <v>3.095532883889973e-05</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0004448843537829816</v>
+        <v>9.806408343138173e-07</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0020185811445117</v>
+        <v>2.97608130495064e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0007755676633678377</v>
+        <v>2.016096732404549e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.005135728511959314</v>
+        <v>8.641696695121937e-06</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.00179364113137126</v>
+        <v>1.523469472886063e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002064248779788613</v>
+        <v>7.752718374831602e-06</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002646105131134391</v>
+        <v>1.382535265292972e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.00236226711422205</v>
+        <v>3.431257709962665e-06</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.005958163179457188</v>
+        <v>2.510531339794397e-05</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001753883785568178</v>
+        <v>2.354545358684845e-07</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001155760954134166</v>
+        <v>2.634687189129181e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0004572017933242023</v>
+        <v>8.65219953993801e-06</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001342180650681257</v>
+        <v>1.09975326267886e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.001134919002652168</v>
+        <v>2.492169414836098e-06</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0005072238272987306</v>
+        <v>5.139687800692627e-06</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001294140936806798</v>
+        <v>5.68189398109098e-06</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.002526717493310571</v>
+        <v>1.060583053913433e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0002360169892199337</v>
+        <v>2.436504473735113e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.004687568172812462</v>
+        <v>2.876761936931871e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.005120698362588882</v>
+        <v>2.76207738352241e-05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.005189672578126192</v>
+        <v>7.080207524268189e-06</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.004640527069568634</v>
+        <v>8.577699190936983e-06</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001843748963437974</v>
+        <v>1.012887423712527e-06</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.007034984417259693</v>
+        <v>1.676218380453065e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0003111375553999096</v>
+        <v>4.805306161870249e-06</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.002076455391943455</v>
+        <v>4.71193743578624e-06</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.004695722833275795</v>
+        <v>2.82193832390476e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.00168502563610673</v>
+        <v>3.504608230286976e-06</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.003632847219705582</v>
+        <v>2.959416087833233e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0003172481374349445</v>
+        <v>9.010588655655738e-06</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.001630324521102011</v>
+        <v>1.316464476985857e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0009378233808092773</v>
+        <v>4.868772521149367e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0003028493374586105</v>
+        <v>1.01647992778453e-06</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001005950500257313</v>
+        <v>8.254430213128217e-06</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001656728680245578</v>
+        <v>1.094223625841551e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.005050260573625565</v>
+        <v>1.928014899021946e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001603572512976825</v>
+        <v>1.6493762814207e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.009802363812923431</v>
+        <v>1.127381256083027e-05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.003584602847695351</v>
+        <v>2.644580854394007e-05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.001271612476557493</v>
+        <v>2.128884807461873e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0026504579000175</v>
+        <v>2.037000194832217e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.005345825105905533</v>
+        <v>2.502660754544195e-05</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0004903836525045335</v>
+        <v>2.619983661134029e-06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.006376400589942932</v>
+        <v>3.86342117053573e-06</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.003207990201190114</v>
+        <v>1.649419755267445e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001420892775058746</v>
+        <v>6.711024980177172e-06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003536270232871175</v>
+        <v>5.443786449177423e-06</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0005541950231418014</v>
+        <v>1.046615670929896e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.00560850091278553</v>
+        <v>2.252120066259522e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001042640302330256</v>
+        <v>1.622535819478799e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0005614255205728114</v>
+        <v>1.018649072648259e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.002277563791722059</v>
+        <v>3.383714283700101e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.002603365341201425</v>
+        <v>2.178994463974959e-06</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0003541882033459842</v>
+        <v>1.561918907100335e-06</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.007760385517030954</v>
+        <v>9.516009413346183e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.001366734737530351</v>
+        <v>2.003708459596965e-06</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.004444103222340345</v>
+        <v>1.188726287182362e-06</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0003719727974385023</v>
+        <v>3.262171958340332e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0005333383451215923</v>
+        <v>6.788717655581422e-06</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001354133244603872</v>
+        <v>4.229852493153885e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0006259412039071321</v>
+        <v>2.607397800602484e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.000644828483927995</v>
+        <v>1.368673656543251e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.002800066489726305</v>
+        <v>1.091784452000866e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0009475233964622021</v>
+        <v>1.217231329064816e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0009349374449811876</v>
+        <v>2.794551983242854e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.002227348042652011</v>
+        <v>7.167551302700303e-06</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0003294248890597373</v>
+        <v>2.201680399593897e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.00179193401709199</v>
+        <v>1.30365401673771e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.00170365534722805</v>
+        <v>1.258287852579087e-06</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004267999611329287</v>
+        <v>5.533712283067871e-06</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.003287344239652157</v>
+        <v>5.311786480888259e-06</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.004127353429794312</v>
+        <v>2.537006912461948e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.00128454458899796</v>
+        <v>1.030984003591584e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.004626742098480463</v>
+        <v>1.484137646912131e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.003313605673611164</v>
+        <v>1.573532608745154e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.009986243210732937</v>
+        <v>1.688191696302965e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0003650015569292009</v>
+        <v>6.140885489003267e-06</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.002369961235672235</v>
+        <v>4.958234057994559e-06</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001076393644325435</v>
+        <v>1.918899761221837e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001910591498017311</v>
+        <v>3.964146628732124e-07</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.00482993246987462</v>
+        <v>2.690330256882589e-05</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0007938779890537262</v>
+        <v>7.854587238398381e-07</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.002299305517226458</v>
+        <v>2.774903987301514e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0001653119397815317</v>
+        <v>9.036163646669593e-06</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.001943677663803101</v>
+        <v>1.11312183435075e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.001165404682978988</v>
+        <v>4.218029062030837e-06</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0001617555390112102</v>
+        <v>7.179940439527854e-06</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.001281428267247975</v>
+        <v>9.091358151636086e-06</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0004865532973781228</v>
+        <v>1.705582917566062e-06</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.002732644323259592</v>
+        <v>1.504915599070955e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.001445732545107603</v>
+        <v>1.112129484681645e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.00333893671631813</v>
+        <v>2.281311208207626e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.000390443135984242</v>
+        <v>8.768178304308094e-06</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0003709225566126406</v>
+        <v>2.476576810295228e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.00186355912592262</v>
+        <v>1.087447526515462e-05</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.001042570685967803</v>
+        <v>1.183830227091676e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.00367398839443922</v>
+        <v>1.351944774796721e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.003557763062417507</v>
+        <v>6.466003924288088e-06</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.007445242255926132</v>
+        <v>1.549485023133457e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0007255185046233237</v>
+        <v>1.120511205954244e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.007559284567832947</v>
+        <v>3.012209890584927e-05</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.01067735441029072</v>
+        <v>1.058884663507342e-06</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.001499499659985304</v>
+        <v>2.421851786493789e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0003740255779121071</v>
+        <v>4.634667220670963e-06</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.002227746415883303</v>
+        <v>1.737363345455378e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.002325232373550534</v>
+        <v>2.579421015980188e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.003079683752730489</v>
+        <v>3.129362539766589e-06</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.003102490678429604</v>
+        <v>1.334200896963011e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.003963207826018333</v>
+        <v>1.049431739374995e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.002568443771451712</v>
+        <v>2.555682112870272e-05</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.005432525649666786</v>
+        <v>2.89497238554759e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.003618390997871757</v>
+        <v>1.041447649186011e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.005620621610432863</v>
+        <v>1.817747397581115e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.001151189673691988</v>
+        <v>1.158863142336486e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.001972988247871399</v>
+        <v>4.940081907989224e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3.541967817000113e-05</v>
+        <v>0.0007047960534691811</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0003107047523371875</v>
+        <v>0.0008462197729386389</v>
       </c>
       <c r="C5" t="n">
-        <v>1.998073275899515e-05</v>
+        <v>0.0001947425480466336</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001245899911737069</v>
+        <v>0.0005748748080804944</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001226996391778812</v>
+        <v>0.0001528798165963963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001763197215041146</v>
+        <v>0.0006745188147760928</v>
       </c>
       <c r="G5" t="n">
-        <v>2.528729964978993e-05</v>
+        <v>0.0001704499591141939</v>
       </c>
       <c r="H5" t="n">
-        <v>5.53932404727675e-05</v>
+        <v>0.0004773926048073918</v>
       </c>
       <c r="I5" t="n">
-        <v>1.695561513770372e-05</v>
+        <v>0.0001795418793335557</v>
       </c>
       <c r="J5" t="n">
-        <v>2.229630626970902e-05</v>
+        <v>0.0007591919857077301</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00030316854827106</v>
+        <v>0.0009842653525993228</v>
       </c>
       <c r="L5" t="n">
-        <v>4.976378113497049e-05</v>
+        <v>0.0003275116323493421</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001472238509450108</v>
+        <v>0.0002943227882497013</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001707871415419504</v>
+        <v>0.0005118156550452113</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002240404282929376</v>
+        <v>0.0007450892007909715</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000138228788273409</v>
+        <v>4.066839028382674e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.156973490258679e-05</v>
+        <v>3.934512642445043e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.70244997611735e-05</v>
+        <v>0.0005060499534010887</v>
       </c>
       <c r="S5" t="n">
-        <v>3.565324732335284e-05</v>
+        <v>8.098679245449603e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>6.936389399925247e-05</v>
+        <v>0.0001228206674568355</v>
       </c>
       <c r="U5" t="n">
-        <v>3.934139022021554e-05</v>
+        <v>0.0002343601372558624</v>
       </c>
       <c r="V5" t="n">
-        <v>1.488059024268296e-05</v>
+        <v>0.0002529647317714989</v>
       </c>
       <c r="W5" t="n">
-        <v>4.867220195592381e-05</v>
+        <v>0.0001431558339390904</v>
       </c>
       <c r="X5" t="n">
-        <v>6.213466258486733e-05</v>
+        <v>0.0001064168682205491</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.289945991331479e-06</v>
+        <v>4.652933057514019e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.70140117208939e-05</v>
+        <v>0.0002510684134904295</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.889198862656485e-06</v>
+        <v>0.0001121747336583212</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.407084972830489e-05</v>
+        <v>0.0001281200529774651</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.583156234933995e-05</v>
+        <v>9.869469795376062e-05</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.946645877789706e-05</v>
+        <v>3.285289858467877e-05</v>
       </c>
       <c r="AE5" t="n">
-        <v>6.522960029542446e-05</v>
+        <v>0.0002900269173551351</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.667177462484688e-05</v>
+        <v>0.0003106100193690509</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.755387271870859e-05</v>
+        <v>5.374343891162425e-05</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.039073196006939e-05</v>
+        <v>0.0001645402953727171</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.146609378745779e-05</v>
+        <v>0.0003235059266444296</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.530224032350816e-05</v>
+        <v>0.0001307705242652446</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.281257937080227e-06</v>
+        <v>0.0001384055794915184</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.469738193321973e-05</v>
+        <v>0.000161904827109538</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.262515045003965e-05</v>
+        <v>0.0003301790857221931</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.908920603455044e-05</v>
+        <v>0.0002455659850966185</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.719986802432686e-05</v>
+        <v>4.581251414492726e-05</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.025604357593693e-05</v>
+        <v>0.0001072212107828818</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.172974538756534e-05</v>
+        <v>6.496087007690221e-05</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.015741175564472e-06</v>
+        <v>9.976184810511768e-05</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.945641088241246e-05</v>
+        <v>4.682049620896578e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.599861808354035e-05</v>
+        <v>0.0003557286690920591</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0001849670516094193</v>
+        <v>0.0007146056741476059</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.688720996957272e-05</v>
+        <v>0.0001507865817984566</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.326324026100338e-05</v>
+        <v>2.160607982659712e-05</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.521152757457457e-05</v>
+        <v>8.520241681253538e-05</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.882223245454952e-05</v>
+        <v>0.0002990135981235653</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0001303151075262576</v>
+        <v>1.87296809599502e-05</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.694409264833666e-05</v>
+        <v>0.0001834492286434397</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.075225196080282e-05</v>
+        <v>0.0001758481957949698</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.65974847227335e-05</v>
+        <v>8.376427285838872e-05</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0001327609788859263</v>
+        <v>0.0001082849776139483</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.463944772694958e-05</v>
+        <v>0.0001913938176585361</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.368722860206617e-05</v>
+        <v>0.0003752696793526411</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0001925681863212958</v>
+        <v>1.609671380720101e-05</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.691134619060904e-05</v>
+        <v>0.0001883277727756649</v>
       </c>
       <c r="BI5" t="n">
-        <v>5.344902456272393e-05</v>
+        <v>9.694528125692159e-05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4.184093995718285e-05</v>
+        <v>0.0004086667904630303</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.874126246548258e-05</v>
+        <v>5.04224699398037e-05</v>
       </c>
       <c r="BL5" t="n">
-        <v>6.035135447746143e-05</v>
+        <v>7.107450073817745e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.117776577710174e-05</v>
+        <v>0.000313059106701985</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.718912972137332e-05</v>
+        <v>1.705507929727901e-05</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.330461135599762e-05</v>
+        <v>9.118069283431396e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>6.408449280570494e-06</v>
+        <v>0.0001839144824771211</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.442894219711889e-05</v>
+        <v>0.0002947211905848235</v>
       </c>
       <c r="BR5" t="n">
-        <v>3.448236384429038e-05</v>
+        <v>0.0003432644298300147</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.880167266994249e-05</v>
+        <v>2.557192601670977e-06</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.584207873558626e-06</v>
+        <v>0.0002172497770516202</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.164349568076432e-05</v>
+        <v>0.0001404986396664754</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0001043062802636996</v>
+        <v>0.0006133539136499166</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.184240298054647e-06</v>
+        <v>0.0002256420266348869</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.446995106060058e-05</v>
+        <v>0.0002187858335673809</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.786683787941001e-05</v>
+        <v>8.437757787760347e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.851823410310317e-05</v>
+        <v>0.0002549157070461661</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.589242548216134e-05</v>
+        <v>0.0001040388888213784</v>
       </c>
       <c r="CB5" t="n">
-        <v>2.523604780435562e-05</v>
+        <v>9.637411130825058e-05</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.518214412499219e-05</v>
+        <v>0.000182754170964472</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.29253512568539e-05</v>
+        <v>0.0003435590188018978</v>
       </c>
       <c r="CE5" t="n">
-        <v>5.539102858165279e-05</v>
+        <v>0.0002318109181942418</v>
       </c>
       <c r="CF5" t="n">
-        <v>1.839197284425609e-05</v>
+        <v>4.426275336300023e-05</v>
       </c>
       <c r="CG5" t="n">
-        <v>1.831619738368317e-05</v>
+        <v>0.000162286261911504</v>
       </c>
       <c r="CH5" t="n">
-        <v>4.285507202439476e-06</v>
+        <v>0.0001656643289607018</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.782364779501222e-05</v>
+        <v>0.0001854384609032422</v>
       </c>
       <c r="CJ5" t="n">
-        <v>4.19290954596363e-05</v>
+        <v>0.0001306969352299348</v>
       </c>
       <c r="CK5" t="n">
-        <v>2.249304543511244e-06</v>
+        <v>3.772762647713535e-05</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.356868753849994e-05</v>
+        <v>3.017714334418997e-06</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.934402618848253e-05</v>
+        <v>0.0002206683275289834</v>
       </c>
       <c r="CN5" t="n">
-        <v>5.681145921698771e-05</v>
+        <v>0.0002899673127103597</v>
       </c>
       <c r="CO5" t="n">
-        <v>4.518768037087284e-06</v>
+        <v>0.0001594730856595561</v>
       </c>
       <c r="CP5" t="n">
-        <v>3.83694568881765e-05</v>
+        <v>7.616050424985588e-05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.80263214133447e-05</v>
+        <v>0.0002229110396001488</v>
       </c>
       <c r="CR5" t="n">
-        <v>4.665182132157497e-05</v>
+        <v>3.864348764182068e-05</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.752674668561667e-05</v>
+        <v>0.0001925525575643405</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0001428554824087769</v>
+        <v>0.0001340756862191483</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.013945893646451e-05</v>
+        <v>1.972581048903521e-05</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.15224784167367e-05</v>
+        <v>0.0002918201789725572</v>
       </c>
       <c r="CW5" t="n">
-        <v>4.475515379454009e-05</v>
+        <v>0.0001700734137557447</v>
       </c>
       <c r="CX5" t="n">
-        <v>5.562046226259554e-06</v>
+        <v>4.268663906259462e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.565247632446699e-05</v>
+        <v>0.0001483842934248969</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.363039584452054e-06</v>
+        <v>0.0001461406500311568</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.975012648676056e-05</v>
+        <v>0.0001735808327794075</v>
       </c>
       <c r="DB5" t="n">
-        <v>2.35734878515359e-05</v>
+        <v>8.434416668023914e-05</v>
       </c>
       <c r="DC5" t="n">
-        <v>3.710409146151505e-06</v>
+        <v>6.07347501500044e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.023779416049365e-05</v>
+        <v>2.639443664520513e-05</v>
       </c>
       <c r="DE5" t="n">
-        <v>4.218315007165074e-05</v>
+        <v>9.960029274225235e-05</v>
       </c>
       <c r="DF5" t="n">
-        <v>8.119027188513428e-05</v>
+        <v>0.000105778563010972</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0001012110515148379</v>
+        <v>9.170790144708008e-05</v>
       </c>
       <c r="DH5" t="n">
-        <v>7.973218453116715e-05</v>
+        <v>0.0002054708602372557</v>
       </c>
       <c r="DI5" t="n">
-        <v>3.25044929923024e-05</v>
+        <v>0.0003696966450661421</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.348209040472284e-05</v>
+        <v>0.0001689087075646967</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.776629743399099e-05</v>
+        <v>3.950491372961551e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>8.564888048567809e-06</v>
+        <v>0.0002723799843806773</v>
       </c>
       <c r="DM5" t="n">
-        <v>9.139724170381669e-06</v>
+        <v>0.000152497086673975</v>
       </c>
       <c r="DN5" t="n">
-        <v>4.232208539178828e-06</v>
+        <v>9.219062485499308e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>4.0495546272723e-05</v>
+        <v>0.0001302577584283426</v>
       </c>
       <c r="DP5" t="n">
-        <v>1.733074714138638e-05</v>
+        <v>0.0001973096805159003</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0001412290439475328</v>
+        <v>0.0002468375896569341</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.083268115413375e-05</v>
+        <v>3.222132727387361e-05</v>
       </c>
       <c r="DS5" t="n">
-        <v>8.436655480181798e-05</v>
+        <v>0.0003002652083523571</v>
       </c>
       <c r="DT5" t="n">
-        <v>3.462758832029067e-05</v>
+        <v>9.888970089377835e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>3.965291034546681e-05</v>
+        <v>0.0002224515774287283</v>
       </c>
       <c r="DV5" t="n">
-        <v>8.868018994689919e-06</v>
+        <v>0.0002082365535898134</v>
       </c>
       <c r="DW5" t="n">
-        <v>2.056804805761203e-05</v>
+        <v>0.000117108240374364</v>
       </c>
       <c r="DX5" t="n">
-        <v>5.134407729201484e-06</v>
+        <v>1.25880069390405e-06</v>
       </c>
       <c r="DY5" t="n">
-        <v>1.161883210443193e-05</v>
+        <v>7.227664900710806e-05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0001146219583461061</v>
+        <v>6.102629777160473e-05</v>
       </c>
       <c r="EA5" t="n">
-        <v>3.119289613096043e-05</v>
+        <v>0.000201797069166787</v>
       </c>
       <c r="EB5" t="n">
-        <v>7.02956021996215e-05</v>
+        <v>0.0003630934224929661</v>
       </c>
       <c r="EC5" t="n">
-        <v>6.601349014090374e-05</v>
+        <v>0.0001091048325179145</v>
       </c>
       <c r="ED5" t="n">
-        <v>8.470225293422118e-05</v>
+        <v>2.440045591356466e-06</v>
       </c>
       <c r="EE5" t="n">
-        <v>3.190201459801756e-05</v>
+        <v>0.0003391730424482375</v>
       </c>
       <c r="EF5" t="n">
-        <v>5.707634500140557e-06</v>
+        <v>0.000336941855493933</v>
       </c>
       <c r="EG5" t="n">
-        <v>4.63997530459892e-05</v>
+        <v>7.429350080201402e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>2.193456566601526e-05</v>
+        <v>0.0001097291969927028</v>
       </c>
       <c r="EI5" t="n">
-        <v>7.823510532034561e-05</v>
+        <v>7.31224354240112e-05</v>
       </c>
       <c r="EJ5" t="n">
-        <v>2.924658474512398e-05</v>
+        <v>0.0002001851389650255</v>
       </c>
       <c r="EK5" t="n">
-        <v>1.592681428519427e-06</v>
+        <v>0.0001391061523463577</v>
       </c>
       <c r="EL5" t="n">
-        <v>8.038096711970866e-05</v>
+        <v>2.775800385279581e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>1.95505181181943e-05</v>
+        <v>8.242942385550123e-06</v>
       </c>
       <c r="EN5" t="n">
-        <v>3.581922101147939e-06</v>
+        <v>2.237270018667914e-05</v>
       </c>
       <c r="EO5" t="n">
-        <v>2.07493758352939e-06</v>
+        <v>0.0002050374168902636</v>
       </c>
       <c r="EP5" t="n">
-        <v>6.833930456195958e-06</v>
+        <v>0.00011789049312938</v>
       </c>
       <c r="EQ5" t="n">
-        <v>2.309736009920016e-05</v>
+        <v>7.32188273104839e-05</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.544564970070496e-05</v>
+        <v>0.0002535625826567411</v>
       </c>
       <c r="ES5" t="n">
-        <v>6.610061245737597e-05</v>
+        <v>0.0003284260747022927</v>
       </c>
       <c r="ET5" t="n">
-        <v>8.393442840315402e-05</v>
+        <v>0.0002506766468286514</v>
       </c>
       <c r="EU5" t="n">
-        <v>1.815553332562558e-06</v>
+        <v>2.105661042151041e-05</v>
       </c>
       <c r="EV5" t="n">
-        <v>4.899487976217642e-05</v>
+        <v>5.8680943766376e-05</v>
       </c>
       <c r="EW5" t="n">
-        <v>1.677787963672017e-06</v>
+        <v>0.0003361331473570317</v>
       </c>
       <c r="EX5" t="n">
-        <v>8.919871106627397e-06</v>
+        <v>0.000364720297511667</v>
       </c>
       <c r="EY5" t="n">
-        <v>4.650670598493889e-05</v>
+        <v>0.0002365262334933504</v>
       </c>
       <c r="EZ5" t="n">
-        <v>1.254434573638719e-05</v>
+        <v>1.663034709054045e-06</v>
       </c>
       <c r="FA5" t="n">
-        <v>1.132337001763517e-05</v>
+        <v>0.0001467600523028523</v>
       </c>
       <c r="FB5" t="n">
-        <v>1.384091228828765e-05</v>
+        <v>0.0001741154119372368</v>
       </c>
       <c r="FC5" t="n">
-        <v>3.213602758478373e-05</v>
+        <v>0.0001521971280453727</v>
       </c>
       <c r="FD5" t="n">
-        <v>2.959631456178613e-05</v>
+        <v>0.0001113003672799096</v>
       </c>
       <c r="FE5" t="n">
-        <v>1.611986408533994e-05</v>
+        <v>3.726637078216299e-05</v>
       </c>
       <c r="FF5" t="n">
-        <v>2.687961386982352e-05</v>
+        <v>0.0001042657968355343</v>
       </c>
       <c r="FG5" t="n">
-        <v>2.072976349154487e-05</v>
+        <v>0.0001524948165751994</v>
       </c>
       <c r="FH5" t="n">
-        <v>4.18496856582351e-05</v>
+        <v>0.000286657945252955</v>
       </c>
       <c r="FI5" t="n">
-        <v>2.157227072530077e-06</v>
+        <v>9.173675061902031e-05</v>
       </c>
       <c r="FJ5" t="n">
-        <v>9.769141615834087e-05</v>
+        <v>0.0002714638249017298</v>
       </c>
       <c r="FK5" t="n">
-        <v>9.225351095665246e-05</v>
+        <v>0.0001777091092662886</v>
       </c>
       <c r="FL5" t="n">
-        <v>4.695779352914542e-05</v>
+        <v>0.000193554544239305</v>
       </c>
       <c r="FM5" t="n">
-        <v>3.783782085520215e-05</v>
+        <v>0.0001629075850360096</v>
       </c>
       <c r="FN5" t="n">
-        <v>9.960572060663253e-05</v>
+        <v>0.0005080322152934968</v>
       </c>
       <c r="FO5" t="n">
-        <v>2.067788227577694e-05</v>
+        <v>8.976043318398297e-06</v>
       </c>
       <c r="FP5" t="n">
-        <v>1.669722769293003e-05</v>
+        <v>0.0002234179701190442</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001272044464712963</v>
+        <v>0.0004708532360382378</v>
       </c>
       <c r="FR5" t="n">
-        <v>5.243807754595764e-05</v>
+        <v>0.0002607752976473421</v>
       </c>
       <c r="FS5" t="n">
-        <v>8.666916255606338e-05</v>
+        <v>2.95318186545046e-05</v>
       </c>
       <c r="FT5" t="n">
-        <v>1.999183587031439e-05</v>
+        <v>0.0001352517865598202</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001027406397042796</v>
+        <v>9.605313971405849e-05</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0001056103574228473</v>
+        <v>0.0001992430916288868</v>
       </c>
       <c r="FW5" t="n">
-        <v>4.59452421637252e-05</v>
+        <v>3.539654062478803e-05</v>
       </c>
       <c r="FX5" t="n">
-        <v>8.306626114062965e-05</v>
+        <v>0.0002906149602495134</v>
       </c>
       <c r="FY5" t="n">
-        <v>5.00653732160572e-05</v>
+        <v>0.0002972381189465523</v>
       </c>
       <c r="FZ5" t="n">
-        <v>5.404998591984622e-05</v>
+        <v>0.0001037452602759004</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0001244527520611882</v>
+        <v>0.0001526321284472942</v>
       </c>
       <c r="GB5" t="n">
-        <v>1.163462366093881e-05</v>
+        <v>0.0003187177062500268</v>
       </c>
       <c r="GC5" t="n">
-        <v>5.931644773227163e-05</v>
+        <v>0.0001644813164602965</v>
       </c>
       <c r="GD5" t="n">
-        <v>2.545145980548114e-05</v>
+        <v>0.0001609185128472745</v>
       </c>
       <c r="GE5" t="n">
-        <v>3.524846761138178e-05</v>
+        <v>6.089312955737114e-05</v>
       </c>
       <c r="GF5" t="n">
-        <v>7.725015166215599e-05</v>
+        <v>5.968448385829106e-05</v>
       </c>
       <c r="GG5" t="n">
-        <v>2.242432674393058e-05</v>
+        <v>0.0004553228209260851</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.3776158690452576</v>
+        <v>9.662898082751781e-05</v>
       </c>
       <c r="B7" t="n">
-        <v>2.432767629623413</v>
+        <v>0.001579349394887686</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1377491652965546</v>
+        <v>0.0004589835298247635</v>
       </c>
       <c r="D7" t="n">
-        <v>1.027340054512024</v>
+        <v>0.0009760985849425197</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04939290881156921</v>
+        <v>0.0001842167839640751</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7249276041984558</v>
+        <v>0.0001682233560131863</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1422631144523621</v>
+        <v>0.0006000202847644687</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2228343188762665</v>
+        <v>0.0005661531467922032</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08636242896318436</v>
+        <v>7.515871402574703e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5925886631011963</v>
+        <v>0.000410506792832166</v>
       </c>
       <c r="K7" t="n">
-        <v>1.665263295173645</v>
+        <v>0.001589255407452583</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1082439795136452</v>
+        <v>0.0006609100382775068</v>
       </c>
       <c r="M7" t="n">
-        <v>0.938554048538208</v>
+        <v>0.001448073424398899</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2275305688381195</v>
+        <v>0.0004612462653312832</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9435400366783142</v>
+        <v>1.985034941753838e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1583076864480972</v>
+        <v>0.0006793570937588811</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1192763298749924</v>
+        <v>1.171196345239878e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1383813321590424</v>
+        <v>7.264601299539208e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0400703102350235</v>
+        <v>0.0001228259352501482</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2048669457435608</v>
+        <v>2.429826054139994e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1637360155582428</v>
+        <v>0.0001348916121060029</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3992013037204742</v>
+        <v>1.664416231506038e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2050991207361221</v>
+        <v>0.0002639702870510519</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03267652913928032</v>
+        <v>0.0002825655683409423</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2074780613183975</v>
+        <v>0.0001006350576062687</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3014176189899445</v>
+        <v>0.0004204191791359335</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.295303076505661</v>
+        <v>0.0005120781133882701</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02128574252128601</v>
+        <v>0.0002843347610905766</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3220609724521637</v>
+        <v>5.216984573053196e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1288753300905228</v>
+        <v>0.0002035652287304401</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1955288052558899</v>
+        <v>0.0002204686607001349</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1417673677206039</v>
+        <v>0.0003065215132664889</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.1912495344877243</v>
+        <v>0.0003308569139335304</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.08205228298902512</v>
+        <v>2.167765342164785e-05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.008945774286985397</v>
+        <v>0.0001890151470433921</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.20538030564785</v>
+        <v>5.26215007994324e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.1545605510473251</v>
+        <v>8.79852450452745e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2273218780755997</v>
+        <v>0.0004373224801383913</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.1034563556313515</v>
+        <v>0.0001336392742814496</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.2098180055618286</v>
+        <v>0.0002088270121021196</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1169680580496788</v>
+        <v>7.054388697724789e-05</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.3171998560428619</v>
+        <v>0.0003474703116808087</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.05720622837543488</v>
+        <v>0.0001485671673435718</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.03484007343649864</v>
+        <v>0.0001846002851380035</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1727947294712067</v>
+        <v>0.0002040633698925376</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1851565986871719</v>
+        <v>0.0002926329034380615</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.623558402061462</v>
+        <v>0.001037134556099772</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.02951926924288273</v>
+        <v>0.0001488176785642281</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1723265945911407</v>
+        <v>0.0006290512974373996</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.357533872127533</v>
+        <v>0.001142030698247254</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.02100665494799614</v>
+        <v>0.0001084595787688158</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.01549799367785454</v>
+        <v>8.874152990756556e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.2398745566606522</v>
+        <v>0.0001170732430182397</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.3846845924854279</v>
+        <v>7.715434185229242e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.2991101145744324</v>
+        <v>0.0001093186583602801</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.3500378727912903</v>
+        <v>0.0002916414523497224</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.4080423414707184</v>
+        <v>0.0002890411415137351</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1664492785930634</v>
+        <v>0.0001868226390797645</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.5873063802719116</v>
+        <v>0.0005394753534346819</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.371997743844986</v>
+        <v>5.582185258390382e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.2084099948406219</v>
+        <v>0.0001432048593414947</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.3094754815101624</v>
+        <v>0.0006367892492562532</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.007689099758863449</v>
+        <v>1.330181839875877e-05</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.2000355422496796</v>
+        <v>2.493918145773932e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.2762524485588074</v>
+        <v>1.625141158001497e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.08904419839382172</v>
+        <v>0.0001454550656490028</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.4090407192707062</v>
+        <v>0.0001090972655219957</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08799132704734802</v>
+        <v>0.0001117988722398877</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.08194325864315033</v>
+        <v>1.910887294798158e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.100115492939949</v>
+        <v>6.148389365989715e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.005324227269738913</v>
+        <v>0.0002235942520201206</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1030749157071114</v>
+        <v>9.813326323637739e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.1046774759888649</v>
+        <v>0.0002176059497287497</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.798113226890564</v>
+        <v>0.0005488635506480932</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1468707472085953</v>
+        <v>0.0001072915911208838</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1518487632274628</v>
+        <v>0.0006278721848502755</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.04634997621178627</v>
+        <v>0.000431341934017837</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.3602012395858765</v>
+        <v>0.0004520463990047574</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1394263505935669</v>
+        <v>0.0002630336384754628</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.009800396859645844</v>
+        <v>0.0001579659292474389</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.311439573764801</v>
+        <v>0.0003286940627731383</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1466134786605835</v>
+        <v>6.973538256715983e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.4001210331916809</v>
+        <v>0.0004256929969415069</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.2119027078151703</v>
+        <v>0.0001732064411044121</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.08458603918552399</v>
+        <v>0.0004022444481961429</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.1080763638019562</v>
+        <v>1.718571002129465e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.175819531083107</v>
+        <v>2.782987394311931e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.06081545352935791</v>
+        <v>5.434588820207864e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0502755381166935</v>
+        <v>1.650375816097949e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1845317929983139</v>
+        <v>8.832089952193201e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.1058748662471771</v>
+        <v>0.0001673307997407392</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.02632248215377331</v>
+        <v>0.0001180442413897254</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1823500692844391</v>
+        <v>0.0002624496701173484</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.3391688764095306</v>
+        <v>0.0007283331360667944</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.2550298869609833</v>
+        <v>0.0001794331183191389</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.257055252790451</v>
+        <v>0.0002950930793303996</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.2344764024019241</v>
+        <v>5.2655566832982e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.2121576815843582</v>
+        <v>0.0002811646845657378</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.09669769555330276</v>
+        <v>0.0002355377655476332</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.1274245828390121</v>
+        <v>4.458644980331883e-05</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.3192595839500427</v>
+        <v>0.0004396965669002384</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.2063486725091934</v>
+        <v>0.0001407203089911491</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2251554578542709</v>
+        <v>0.0004496652400121093</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.1202180087566376</v>
+        <v>5.743474321207032e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.2001779079437256</v>
+        <v>2.43119866354391e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.08287952840328217</v>
+        <v>8.792823791736737e-05</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.09762745350599289</v>
+        <v>4.781536335940473e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.1217824518680573</v>
+        <v>0.0001521057856734842</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1468281447887421</v>
+        <v>1.614348730072379e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.1801897287368774</v>
+        <v>0.000679491669870913</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.09633561968803406</v>
+        <v>0.000150407970068045</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.5062806010246277</v>
+        <v>0.0005150469951331615</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.3112881779670715</v>
+        <v>1.200455881189555e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.1116327568888664</v>
+        <v>0.0007999199442565441</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.1657377779483795</v>
+        <v>0.0002849853772204369</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.1032833755016327</v>
+        <v>0.0004702863516286016</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.01281335949897766</v>
+        <v>0.0002811350277625024</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2906703054904938</v>
+        <v>0.0001603620476089418</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.1623458415269852</v>
+        <v>0.0001355245622107759</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.1652648895978928</v>
+        <v>0.0001161113978014328</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.09520827233791351</v>
+        <v>0.0001644368749111891</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.1391602754592896</v>
+        <v>0.0001202080529765226</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.3180017471313477</v>
+        <v>0.0001467875263188034</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1123420670628548</v>
+        <v>0.0002541635185480118</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.03884297609329224</v>
+        <v>0.0002073049108730629</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.2744668126106262</v>
+        <v>0.0006500690942630172</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1618602126836777</v>
+        <v>2.629368464113213e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.09653088450431824</v>
+        <v>5.452127516036853e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.5221041440963745</v>
+        <v>3.791398194152862e-05</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.04338394105434418</v>
+        <v>0.0003889567451551557</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.2584664225578308</v>
+        <v>4.004508082289249e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.110265389084816</v>
+        <v>0.000176459172507748</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.02729310095310211</v>
+        <v>4.842325870413333e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.1005225479602814</v>
+        <v>0.0007343910983763635</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.03611850365996361</v>
+        <v>0.0005724840448237956</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0006379783153533936</v>
+        <v>0.0001484187814639881</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.2432888150215149</v>
+        <v>0.0004643800784833729</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.02885277941823006</v>
+        <v>1.76891844603233e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02256443537771702</v>
+        <v>0.0003220122307538986</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.003008332569152117</v>
+        <v>2.407520150882192e-05</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.1089785397052765</v>
+        <v>8.629573130747303e-05</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.08977685868740082</v>
+        <v>2.426214632578194e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001020179595798254</v>
+        <v>0.0001396461884723976</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.07930102944374084</v>
+        <v>0.0001424393703928217</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.1564057320356369</v>
+        <v>0.0001249875203939155</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.2754300832748413</v>
+        <v>0.0004236048262100667</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.04095311090350151</v>
+        <v>5.119180423207581e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.3026671409606934</v>
+        <v>0.000184303818969056</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1961964219808578</v>
+        <v>3.866304905386642e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.7380232810974121</v>
+        <v>1.822072954382747e-05</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.1507120877504349</v>
+        <v>0.0001428203831892461</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.2136708050966263</v>
+        <v>4.190531399217434e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.05158383399248123</v>
+        <v>0.0003856864059343934</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.110185943543911</v>
+        <v>4.068317866767757e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.3064840137958527</v>
+        <v>0.0004714316455647349</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.1234926730394363</v>
+        <v>0.0001649931218707934</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.163348987698555</v>
+        <v>0.0004885152447968721</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.1412232518196106</v>
+        <v>1.003793749987381e-05</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.1812475174665451</v>
+        <v>5.768915434600785e-05</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.1311215162277222</v>
+        <v>9.742172551341355e-05</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.04460106045007706</v>
+        <v>1.209349284181371e-05</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.1709513068199158</v>
+        <v>0.000181755778612569</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.07510348409414291</v>
+        <v>1.016775058815256e-05</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.1659756898880005</v>
+        <v>0.0002391285379417241</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.1732337772846222</v>
+        <v>0.0003364705189596862</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1688473969697952</v>
+        <v>0.0001909432176034898</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.09662919491529465</v>
+        <v>4.415677540237084e-05</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.06390085816383362</v>
+        <v>2.254183345939964e-05</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.02485984563827515</v>
+        <v>0.0002330103743588552</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.1233137026429176</v>
+        <v>0.0002283025823999196</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.1902194768190384</v>
+        <v>0.0001364345953334123</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.1846598386764526</v>
+        <v>1.091572630684823e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.180169090628624</v>
+        <v>0.0002633285475894809</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.07741998881101608</v>
+        <v>6.003068119753152e-05</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.2519988119602203</v>
+        <v>0.000475194479804486</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.6496071815490723</v>
+        <v>0.0001193934585899115</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.1469545960426331</v>
+        <v>0.0003316801157779992</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.03327977657318115</v>
+        <v>6.008415221003816e-05</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.1230124905705452</v>
+        <v>0.0001359800808131695</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.1293773800134659</v>
+        <v>0.0005846953135915101</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.3152615427970886</v>
+        <v>0.0003204743552487344</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.1243953630328178</v>
+        <v>0.0001732622040435672</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.2812303900718689</v>
+        <v>6.844417657703161e-05</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.02954638376832008</v>
+        <v>0.0004293865931686014</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.2567750811576843</v>
+        <v>0.000387943786336109</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.1394527554512024</v>
+        <v>0.0001283199526369572</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.7118858695030212</v>
+        <v>0.0003141425549983978</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.06614178419113159</v>
+        <v>0.0001487233530497178</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.1744417399168015</v>
+        <v>0.0002483417629264295</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00282678660005331</v>
+        <v>0.00110991729889065</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01214711926877499</v>
+        <v>0.003950306214392185</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001278288546018302</v>
+        <v>0.002524547511711717</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00499733118340373</v>
+        <v>0.0002922077546827495</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002356437500566244</v>
+        <v>0.0003632815205492079</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004020823165774345</v>
+        <v>0.005275040864944458</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003168248804286122</v>
+        <v>0.000888401351403445</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001012476976029575</v>
+        <v>0.001771027571521699</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001873276312835515</v>
+        <v>0.002638579346239567</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003033562796190381</v>
+        <v>0.0003899318398907781</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007637073751538992</v>
+        <v>0.006298575084656477</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005835294141434133</v>
+        <v>0.002659063087776303</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005964800715446472</v>
+        <v>0.001051664818078279</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003162852488458157</v>
+        <v>2.496363595128059e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005452200304716825</v>
+        <v>0.004037919454276562</v>
       </c>
       <c r="P9" t="n">
-        <v>1.754623372107744e-05</v>
+        <v>9.334887727163732e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00159449886996299</v>
+        <v>3.926051431335509e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009062786120921373</v>
+        <v>0.00259843235835433</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001150560419773683</v>
+        <v>0.0002556130930315703</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001618594047613442</v>
+        <v>0.0008569719502702355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0007776287966407835</v>
+        <v>0.0001308908686041832</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002256995998322964</v>
+        <v>0.0005474056233651936</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0001777498400770128</v>
+        <v>0.0008889128221198916</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001790213631466031</v>
+        <v>0.000109609478386119</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0004721333971247077</v>
+        <v>0.0007443990325555205</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009404245647601783</v>
+        <v>0.0003962978080380708</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0005497938254848123</v>
+        <v>0.0002173724205931649</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0004851696430705488</v>
+        <v>0.0007168914889916778</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002393315313383937</v>
+        <v>0.0001005908125080168</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0009185826638713479</v>
+        <v>0.0009742530528455973</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.002050702460110188</v>
+        <v>0.001270160428248346</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001134692342020571</v>
+        <v>0.00184992840513587</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0004335967532824725</v>
+        <v>0.0009076923015527427</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0002731430577114224</v>
+        <v>0.0002454536152072251</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.560534191317856e-05</v>
+        <v>0.002702944213524461</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0007990081794559956</v>
+        <v>3.012783417943865e-05</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.00187263882253319</v>
+        <v>0.0001816317089833319</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001473414711654186</v>
+        <v>0.001426071859896183</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.12583103752695e-05</v>
+        <v>0.0003350217593833804</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0008405145490542054</v>
+        <v>0.0005495016812346876</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001163752051070333</v>
+        <v>0.0004140056553296745</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001295046880841255</v>
+        <v>0.0007207148591987789</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0008363919332623482</v>
+        <v>0.0005464909481815994</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0005100807175040245</v>
+        <v>0.0009903510799631476</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001086191041395068</v>
+        <v>0.0005159704014658928</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0003231423906981945</v>
+        <v>4.149929736740887e-05</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.008855970576405525</v>
+        <v>0.005534220952540636</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0003176757600158453</v>
+        <v>0.001882480457425117</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001891662599518895</v>
+        <v>0.0005218456499278545</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0005468803574331105</v>
+        <v>0.0005740615888498724</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001093181315809488</v>
+        <v>0.002831150311976671</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.00229442841373384</v>
+        <v>0.0005554909585043788</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001813556766137481</v>
+        <v>0.0009743215050548315</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0007500535575672984</v>
+        <v>0.0001281957956962287</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0005643966724164784</v>
+        <v>0.0001485037500970066</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002219654619693756</v>
+        <v>0.002146437996998429</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001873129629530013</v>
+        <v>0.0002024429850280285</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00103716179728508</v>
+        <v>0.0001778873265720904</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.003255943534895778</v>
+        <v>0.0007328360807150602</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001735564321279526</v>
+        <v>0.0004165057907812297</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.00161698623560369</v>
+        <v>0.0001046848483383656</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002032177522778511</v>
+        <v>0.000845154223497957</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.00121225870680064</v>
+        <v>0.0017410988220945</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001438026782125235</v>
+        <v>0.000271777855232358</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001377628650516272</v>
+        <v>0.0007109728176146746</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0002665815700311214</v>
+        <v>0.0001190224284073338</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0008224219782277942</v>
+        <v>0.000943081162404269</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.00113165401853621</v>
+        <v>0.001310231513343751</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0004071981238666922</v>
+        <v>0.001587257953360677</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.001042727497406304</v>
+        <v>0.001028028666041791</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0005750433192588389</v>
+        <v>0.0004158506344538182</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0002007214643526822</v>
+        <v>0.001248993910849094</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0001588140439707786</v>
+        <v>0.0002248252276331186</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003769607516005635</v>
+        <v>0.003623644821345806</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0009270152077078819</v>
+        <v>0.0002742358483374119</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.00161794014275074</v>
+        <v>0.0004266673640813679</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0007903575315140188</v>
+        <v>0.0001094337785616517</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001749948598444462</v>
+        <v>0.001246469677425921</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0005810654256492853</v>
+        <v>0.0007701380527578294</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0002105312596540898</v>
+        <v>0.0006508599035441875</v>
       </c>
       <c r="CC9" t="n">
-        <v>9.17155557544902e-05</v>
+        <v>0.0001850078551797196</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0006904029287397861</v>
+        <v>0.0004013784928247333</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002172223059460521</v>
+        <v>0.00102571805473417</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0005438000080175698</v>
+        <v>0.000156049121869728</v>
       </c>
       <c r="CG9" t="n">
-        <v>7.546998676843941e-05</v>
+        <v>0.0001084005925804377</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0003584973746910691</v>
+        <v>0.0002802208764478564</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0007391548133455217</v>
+        <v>0.0009071544045582414</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0005257074953988194</v>
+        <v>0.0001471911673434079</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.000270349410129711</v>
+        <v>0.000656325719319284</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0003171080024912953</v>
+        <v>5.429315933724865e-06</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001429508090950549</v>
+        <v>0.0006317025399766862</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0006372425705194473</v>
+        <v>0.0002796337939798832</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001221940503455698</v>
+        <v>0.0009164661169052124</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001661690883338451</v>
+        <v>0.0004046828835271299</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0005664691561833024</v>
+        <v>0.0005381995579227805</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.002188141457736492</v>
+        <v>0.00120124127715826</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001247600768692791</v>
+        <v>9.471671364735812e-05</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001330411643721163</v>
+        <v>0.0005231692921370268</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.001197717385366559</v>
+        <v>0.0001352864201180637</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0005436779465526342</v>
+        <v>5.471252370625734e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001578566036187112</v>
+        <v>0.0009088137885555625</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.000543614907655865</v>
+        <v>0.0003004446334671229</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0007365939673036337</v>
+        <v>1.772661926224828e-05</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0003524433122947812</v>
+        <v>0.0001340211019851267</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0009357305243611336</v>
+        <v>0.001107553951442242</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0005456616054289043</v>
+        <v>0.0002026627480518073</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0003168837283737957</v>
+        <v>0.0007460527122020721</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001173125492641702</v>
+        <v>3.984132490586489e-07</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001070677302777767</v>
+        <v>0.0009342064149677753</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001190796494483948</v>
+        <v>0.0007933187880553305</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0003844320017378777</v>
+        <v>8.748167601879686e-05</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0002268846146762371</v>
+        <v>3.177765756845474e-05</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.003803701605647802</v>
+        <v>4.405606887303293e-05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0002785795950330794</v>
+        <v>0.003568142186850309</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001983416266739368</v>
+        <v>0.0005098703550174832</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0007713079685345292</v>
+        <v>0.001701268833130598</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.00225770752876997</v>
+        <v>0.0009205525275319815</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001358180888928473</v>
+        <v>0.0005818220088258386</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0005458922823891044</v>
+        <v>0.0004850213881582022</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0009954945417121053</v>
+        <v>0.0007433259743265808</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.001703733345493674</v>
+        <v>0.001464340137317777</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0007230310584418476</v>
+        <v>0.0003773283679038286</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.000955849071033299</v>
+        <v>0.0005677837762050331</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001151244738139212</v>
+        <v>0.0007068602717481554</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0006484079640358686</v>
+        <v>0.0007244378793984652</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0006892671808600426</v>
+        <v>0.0005215501878410578</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0007011451525613666</v>
+        <v>0.0003419161075726151</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0001494500029366463</v>
+        <v>0.000227312310016714</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.002493670675903559</v>
+        <v>0.001581570133566856</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.001039473339915276</v>
+        <v>0.0001232167851412669</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001296003232710063</v>
+        <v>0.001365700038149953</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0008461355464532971</v>
+        <v>0.0005752716097049415</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.814815161400475e-05</v>
+        <v>0.0001777692377800122</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.000781796989031136</v>
+        <v>0.0003565711667761207</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0008076783269643784</v>
+        <v>0.001074266969226301</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0004442026547621936</v>
+        <v>0.0005852565518580377</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.000862141780089587</v>
+        <v>0.0002122085279552266</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0002737515605986118</v>
+        <v>0.000649639405310154</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0009496908751316369</v>
+        <v>0.0008265189244411886</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0003754555364139378</v>
+        <v>0.0005405875272117555</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0003428092750255018</v>
+        <v>0.000449315644800663</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0008542544092051685</v>
+        <v>0.0002484856813680381</v>
       </c>
       <c r="EM9" t="n">
-        <v>4.293242091080174e-05</v>
+        <v>0.0003149862750433385</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0001296390692004934</v>
+        <v>0.000369895831681788</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.001085003255866468</v>
+        <v>0.0006482766475528479</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001255032606422901</v>
+        <v>0.000357192155206576</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0003928244404960424</v>
+        <v>0.0002302764041814953</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0002076330274576321</v>
+        <v>0.00100339250639081</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0002933899813797325</v>
+        <v>0.002347049303352833</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.002346933353692293</v>
+        <v>0.002359197707846761</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001108619151636958</v>
+        <v>0.0001087709606508724</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.002605162793770432</v>
+        <v>5.248318484518677e-05</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0004437769530341029</v>
+        <v>0.0002930547052528709</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0004686173924710602</v>
+        <v>0.0001494516473030671</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001608923310413957</v>
+        <v>0.00111836998257786</v>
       </c>
       <c r="EZ9" t="n">
-        <v>9.448238415643573e-06</v>
+        <v>0.0003574846487026662</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.000302627042401582</v>
+        <v>0.0001255215611308813</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0003477452555671334</v>
+        <v>0.0002576892438810319</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.001058947644196451</v>
+        <v>0.0007420568144880235</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0005255797877907753</v>
+        <v>0.0002545457391534001</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.000241115121752955</v>
+        <v>0.0003987086820416152</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0004585124552249908</v>
+        <v>0.0002874608326237649</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0002929235342890024</v>
+        <v>0.0006052941316738725</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001010682317428291</v>
+        <v>0.0014466333668679</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.001048543723300099</v>
+        <v>0.001583309844136238</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.001287188613787293</v>
+        <v>0.001051762024872005</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0003076055727433413</v>
+        <v>0.0002974707458633929</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0001363101328024641</v>
+        <v>0.001448392402380705</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0002336399920750409</v>
+        <v>0.0002566366165410727</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0005165842012502253</v>
+        <v>0.002033719560131431</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0009368159808218479</v>
+        <v>0.001493421266786754</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001471338095143437</v>
+        <v>0.0007839305908419192</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.001208400819450617</v>
+        <v>0.0008556609391234815</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.00214868993498385</v>
+        <v>0.0004833822604268789</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0004516241606324911</v>
+        <v>0.001515745418146253</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.002919914200901985</v>
+        <v>0.001022976939566433</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.002734736073762178</v>
+        <v>0.0006780912517569959</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.001555460854433477</v>
+        <v>0.001092454534955323</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0008556842803955078</v>
+        <v>0.003087291028350592</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0006047050701454282</v>
+        <v>0.001227258006110787</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0009483186295256019</v>
+        <v>0.001126007176935673</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.00116607453674078</v>
+        <v>7.244442531373352e-05</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0003993873833678663</v>
+        <v>0.001155976788140833</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.00141393207013607</v>
+        <v>0.0008075381629168987</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0002842685207724571</v>
+        <v>0.001551581081002951</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0009903607424348593</v>
+        <v>0.0002117014228133485</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.001458918442949653</v>
+        <v>0.0001310461375396699</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0004055703175254166</v>
+        <v>0.0009642558870837092</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0004026203532703221</v>
+        <v>0.000772097846493125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00223468616604805</v>
+        <v>0.002322203945368528</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02058927714824677</v>
+        <v>0.009261196479201317</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001972401514649391</v>
+        <v>0.001204993226565421</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01136930380016565</v>
+        <v>0.005838025361299515</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001892404863610864</v>
+        <v>0.003139236010611057</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005132630933076143</v>
+        <v>0.001090823556296527</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001911272411234677</v>
+        <v>0.004684414248913527</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001576477778144181</v>
+        <v>0.003043793141841888</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002102605532854795</v>
+        <v>0.001283250167034566</v>
       </c>
       <c r="J10" t="n">
-        <v>0.003753960132598877</v>
+        <v>0.003063063602894545</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0147222587838769</v>
+        <v>0.01011528819799423</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001536765339551494</v>
+        <v>0.001912878127768636</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01087088976055384</v>
+        <v>0.008754277601838112</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004080173093825579</v>
+        <v>0.00502995029091835</v>
       </c>
       <c r="O10" t="n">
-        <v>0.007181307766586542</v>
+        <v>0.001082511385902762</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001607812126167119</v>
+        <v>0.004170823842287064</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0009828237816691399</v>
+        <v>0.001071418635547161</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001988774398341775</v>
+        <v>0.001628403435461223</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0007937566842883825</v>
+        <v>0.0009229711722582579</v>
       </c>
       <c r="T10" t="n">
-        <v>0.002105127321556211</v>
+        <v>0.0006880664150230587</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0009952422697097063</v>
+        <v>0.0002734002482611686</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002181557007133961</v>
+        <v>0.0002131790388375521</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001715760445222259</v>
+        <v>1.20006370707415e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001064579817466438</v>
+        <v>0.001952329068444669</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002202722709625959</v>
+        <v>0.001136657549068332</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00178762583527714</v>
+        <v>0.002966565079987049</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001192739349789917</v>
+        <v>0.002298142295330763</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0009317158255726099</v>
+        <v>0.003261247416958213</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.003121329704299569</v>
+        <v>0.000533495272975415</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001707920455373824</v>
+        <v>0.001790536800399423</v>
       </c>
       <c r="AE10" t="n">
-        <v>6.67217536829412e-05</v>
+        <v>6.044312613084912e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0002437480725347996</v>
+        <v>0.003601375734433532</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0001664870942477137</v>
+        <v>0.001663188450038433</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.000726912054233253</v>
+        <v>0.001350472215563059</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0002001427346840501</v>
+        <v>0.0006392348441295326</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.000827317766379565</v>
+        <v>0.0005166358314454556</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.00175955577287823</v>
+        <v>0.001198273617774248</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.00197385810315609</v>
+        <v>0.003179917577654123</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0003776566300075501</v>
+        <v>0.0002377587952651083</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0008244746131822467</v>
+        <v>0.001214613439515233</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0019312200602144</v>
+        <v>0.001028543105348945</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.002157277194783092</v>
+        <v>0.002195205772295594</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0007477683247998357</v>
+        <v>0.001091467100195587</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001542814774438739</v>
+        <v>9.702342504169792e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001326105208136141</v>
+        <v>0.001121438341215253</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.001260609249584377</v>
+        <v>0.002343254163861275</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0152748841792345</v>
+        <v>0.007777693215757608</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0002371010341448709</v>
+        <v>0.001509371213614941</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.003201690735295415</v>
+        <v>0.002149658277630806</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.001233664690516889</v>
+        <v>0.006080332677811384</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0003196292382199317</v>
+        <v>0.001067230245098472</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0006129284738563001</v>
+        <v>0.0002928153844550252</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0004616368096321821</v>
+        <v>0.0007787132635712624</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.001768186106346548</v>
+        <v>0.0003506448701955378</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0007099382928572595</v>
+        <v>0.002273638034239411</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.004062262363731861</v>
+        <v>0.001945315510965884</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.004404742736369371</v>
+        <v>0.0007327876519411802</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.001948613673448563</v>
+        <v>0.001611784566193819</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.004059050232172012</v>
+        <v>0.001447333255782723</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.003730748547241092</v>
+        <v>0.001345699420198798</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002532484941184521</v>
+        <v>0.001212468720041215</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001043431228026748</v>
+        <v>0.003363301046192646</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.001204878673888743</v>
+        <v>0.0009873684030026197</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.001983995549380779</v>
+        <v>0.0004597442748490721</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.003317656693980098</v>
+        <v>0.0004813170526176691</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001686358358711004</v>
+        <v>8.110576891340315e-05</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0007874318398535252</v>
+        <v>0.002040267689153552</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.002588518662378192</v>
+        <v>0.0008243321208283305</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001378883025608957</v>
+        <v>0.0007875312003307045</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0003123088681604713</v>
+        <v>0.001086627482436597</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.998289609327912e-05</v>
+        <v>0.001556230476126075</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.000801857269834727</v>
+        <v>2.325527020730078e-05</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.001454198500141501</v>
+        <v>0.0002066364977508783</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.007264583837240934</v>
+        <v>0.004531390499323606</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001940574031323195</v>
+        <v>3.989634569734335e-05</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.002053624950349331</v>
+        <v>0.004381143487989902</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.000219426307012327</v>
+        <v>0.001437107683159411</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.00281706708483398</v>
+        <v>0.001835094066336751</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0005909667233936489</v>
+        <v>0.001152819604612887</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.001408968819305301</v>
+        <v>0.0007888697437010705</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.001437680446542799</v>
+        <v>0.002145903650671244</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.001018827315419912</v>
+        <v>0.001448690425604582</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.003268859349191189</v>
+        <v>0.002754653338342905</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001510664820671082</v>
+        <v>0.0003672907478176057</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.001122622634284198</v>
+        <v>0.002481661038473248</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0006207629921846092</v>
+        <v>0.0001192821655422449</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001269145403057337</v>
+        <v>0.0001839564938563854</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0007738065905869007</v>
+        <v>0.0003293209010735154</v>
       </c>
       <c r="CK10" t="n">
-        <v>7.068164995871484e-05</v>
+        <v>0.0002075838419841602</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0004044844827149063</v>
+        <v>0.0009261394152417779</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.002922030165791512</v>
+        <v>0.001910096034407616</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001562422490678728</v>
+        <v>0.002985303057357669</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0009674502070993185</v>
+        <v>0.0001868639374151826</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.003066081088036299</v>
+        <v>0.002649118658155203</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.002131226239725947</v>
+        <v>0.0002928883768618107</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.001734055578708649</v>
+        <v>0.000481712631881237</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0022764066234231</v>
+        <v>0.0008605884504504502</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.004081904888153076</v>
+        <v>0.0006960183964110911</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.000340344849973917</v>
+        <v>0.001767495414242148</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0008172590751200914</v>
+        <v>0.00123345002066344</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.002572766272351146</v>
+        <v>0.002775911241769791</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.001819846220314503</v>
+        <v>0.0001513682364020497</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.001958199543878436</v>
+        <v>0.002786263357847929</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0005522726569324732</v>
+        <v>0.0007074569584801793</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.001244521932676435</v>
+        <v>0.0002135460672434419</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0006360188126564026</v>
+        <v>0.0003402561706025153</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0002061033446807414</v>
+        <v>0.0005374179454520345</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0001076142361853272</v>
+        <v>0.001112507074140012</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001732780248858035</v>
+        <v>0.0007755006663501263</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.001681673107668757</v>
+        <v>0.00474905502051115</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001507982378825545</v>
+        <v>8.945469744503498e-05</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.00579746812582016</v>
+        <v>0.003137417603284121</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001182794105261564</v>
+        <v>0.0004272310470696539</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0004858293978031725</v>
+        <v>0.004001291934400797</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.00172003114130348</v>
+        <v>0.002704929560422897</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0003363981668371707</v>
+        <v>0.004662874154746532</v>
       </c>
       <c r="DM10" t="n">
-        <v>2.072699135169387e-05</v>
+        <v>0.001554442686028779</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.001950889243744314</v>
+        <v>0.001238737255334854</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0009560424950905144</v>
+        <v>0.0004918095655739307</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.001415979000739753</v>
+        <v>0.0004062228836119175</v>
       </c>
       <c r="DQ10" t="n">
-        <v>3.192479925928637e-05</v>
+        <v>0.0008419163059443235</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001093819504603744</v>
+        <v>0.0004979338264092803</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.001428557676263154</v>
+        <v>0.001500792452134192</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0001334748085355386</v>
+        <v>0.001362524344585836</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0007309550419449806</v>
+        <v>0.002421463839709759</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0009820502018555999</v>
+        <v>0.004793423227965832</v>
       </c>
       <c r="DW10" t="n">
-        <v>7.763292524032295e-05</v>
+        <v>3.533343624440022e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0001416062004864216</v>
+        <v>0.0006775317015126348</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.00269233132712543</v>
+        <v>0.0005524200387299061</v>
       </c>
       <c r="DZ10" t="n">
-        <v>6.751778710167855e-05</v>
+        <v>0.001797001343220472</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.002448404207825661</v>
+        <v>0.0007649350445717573</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0009410835336893797</v>
+        <v>0.003002438927069306</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0009363579447381198</v>
+        <v>0.000777504057623446</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0004823558265343308</v>
+        <v>0.004277512431144714</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0002274999424116686</v>
+        <v>0.003365472890436649</v>
       </c>
       <c r="EF10" t="n">
-        <v>4.824780626222491e-05</v>
+        <v>0.0003192127915099263</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.002233312930911779</v>
+        <v>0.002887330949306488</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.0007208381430245936</v>
+        <v>0.0001936426851898432</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.001802363200113177</v>
+        <v>0.001685755793005228</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0005603397730737925</v>
+        <v>0.0004468618717510253</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0009781557600945234</v>
+        <v>0.0006949161179363728</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0006617562612518668</v>
+        <v>0.0004685891326516867</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0001631030754651874</v>
+        <v>0.0006806266610510647</v>
       </c>
       <c r="EN10" t="n">
-        <v>2.213998232036829e-05</v>
+        <v>0.0008779149502515793</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.001008722698315978</v>
+        <v>0.001364317955449224</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.002200980903580785</v>
+        <v>0.002340839710086584</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0006847299518994987</v>
+        <v>0.001218387740664184</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.001581901335157454</v>
+        <v>0.002969240769743919</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0009122532210312784</v>
+        <v>0.0002532457001507282</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.005261373706161976</v>
+        <v>0.0006867034826427698</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001612116117030382</v>
+        <v>0.0001389983808621764</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.001920360373333097</v>
+        <v>0.0005885615828447044</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0007630140753462911</v>
+        <v>0.002113895025104284</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0004573640180751681</v>
+        <v>0.001202505198307335</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.002477304078638554</v>
+        <v>0.003196300473064184</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001001446973532438</v>
+        <v>0.0003312627668492496</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001575889415107667</v>
+        <v>0.002797134453430772</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0003180971543770283</v>
+        <v>0.0002150724467355758</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001492761308327317</v>
+        <v>0.0005666924407705665</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0009665148099884391</v>
+        <v>0.0006262232782319188</v>
       </c>
       <c r="FE10" t="n">
-        <v>3.40428960043937e-05</v>
+        <v>6.03624212089926e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0004503274103626609</v>
+        <v>0.001208914909511805</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0001186553272418678</v>
+        <v>0.000598830112721771</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0006234832690097392</v>
+        <v>0.00125431758351624</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0005443256814032793</v>
+        <v>0.002451770007610321</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.001879088464193046</v>
+        <v>0.0005097479443065822</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0008837039931677282</v>
+        <v>0.0004714534152299166</v>
       </c>
       <c r="FL10" t="n">
-        <v>4.128219734411687e-05</v>
+        <v>0.0009482931345701218</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.001003808109089732</v>
+        <v>0.0008805051329545677</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0007389423553831875</v>
+        <v>0.0009720236412249506</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0008027732837945223</v>
+        <v>0.002908235648646951</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.001364748924970627</v>
+        <v>0.0001628673053346574</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.001738214399665594</v>
+        <v>0.001210973947308958</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.00070715177571401</v>
+        <v>0.001096412539482117</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.00148610700853169</v>
+        <v>0.001503382110968232</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.001191010582260787</v>
+        <v>0.0005980781279504299</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0003082117182202637</v>
+        <v>0.002505268435925245</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.001036991365253925</v>
+        <v>0.0001924153475556523</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0002614593249745667</v>
+        <v>0.002972491318359971</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.001256020739674568</v>
+        <v>0.001612702733837068</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.002219863003119826</v>
+        <v>0.003198997583240271</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0009940678719431162</v>
+        <v>0.001721216482110322</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0009871629299595952</v>
+        <v>0.0001021077623590827</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0007021540659479797</v>
+        <v>0.002653039060533047</v>
       </c>
       <c r="GC10" t="n">
-        <v>2.596992999315262e-06</v>
+        <v>0.003163669956848025</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.00144477910362184</v>
+        <v>0.001500559039413929</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.005043922923505306</v>
+        <v>0.001253621187061071</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0009373226203024387</v>
+        <v>0.0022849440574646</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0003499668382573873</v>
+        <v>0.001080205081962049</v>
       </c>
     </row>
     <row r="11">
@@ -6689,1709 +6689,1709 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6.535396668283511e-09</v>
+        <v>2.793313844118295e-11</v>
       </c>
       <c r="B12" t="n">
-        <v>3.916667878911539e-08</v>
+        <v>1.697005036493948e-10</v>
       </c>
       <c r="C12" t="n">
-        <v>3.277594418094054e-09</v>
+        <v>1.224030078683658e-11</v>
       </c>
       <c r="D12" t="n">
-        <v>8.338776069649612e-08</v>
+        <v>4.028782515930196e-12</v>
       </c>
       <c r="E12" t="n">
-        <v>9.770117159746405e-09</v>
+        <v>1.249635256383996e-10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.832260204144177e-09</v>
+        <v>2.120647407677367e-11</v>
       </c>
       <c r="G12" t="n">
-        <v>6.261750229441532e-09</v>
+        <v>4.761003397080188e-11</v>
       </c>
       <c r="H12" t="n">
-        <v>9.756861985010801e-11</v>
+        <v>2.500989346176929e-11</v>
       </c>
       <c r="I12" t="n">
-        <v>3.525455261055299e-09</v>
+        <v>1.696493986957925e-11</v>
       </c>
       <c r="J12" t="n">
-        <v>1.742420607797612e-08</v>
+        <v>7.486452430205404e-12</v>
       </c>
       <c r="K12" t="n">
-        <v>2.218724759472934e-08</v>
+        <v>2.535382459534219e-10</v>
       </c>
       <c r="L12" t="n">
-        <v>9.186259530835628e-10</v>
+        <v>3.962173991678419e-11</v>
       </c>
       <c r="M12" t="n">
-        <v>4.62286848801341e-08</v>
+        <v>8.333941869942407e-11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.394298981300835e-08</v>
+        <v>1.736085303294388e-10</v>
       </c>
       <c r="O12" t="n">
-        <v>1.726206200203251e-08</v>
+        <v>1.387662294100034e-11</v>
       </c>
       <c r="P12" t="n">
-        <v>1.554797535163743e-08</v>
+        <v>1.169081541643746e-12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.543623362465496e-08</v>
+        <v>8.223596109635523e-11</v>
       </c>
       <c r="R12" t="n">
-        <v>1.649613778909043e-11</v>
+        <v>5.587479784407989e-11</v>
       </c>
       <c r="S12" t="n">
-        <v>6.173621613925206e-09</v>
+        <v>2.977724837538442e-12</v>
       </c>
       <c r="T12" t="n">
-        <v>8.737553791604569e-09</v>
+        <v>9.764060220074366e-12</v>
       </c>
       <c r="U12" t="n">
-        <v>4.729927560731539e-09</v>
+        <v>4.067714047539805e-12</v>
       </c>
       <c r="V12" t="n">
-        <v>3.938004144998786e-09</v>
+        <v>2.769825688253569e-11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.741357102957863e-08</v>
+        <v>4.002269349268062e-11</v>
       </c>
       <c r="X12" t="n">
-        <v>9.594865346684855e-09</v>
+        <v>9.893840954844357e-12</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.688111067072896e-08</v>
+        <v>3.657918065669286e-11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.186896581018004e-09</v>
+        <v>2.362257091326203e-12</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.995685085722016e-09</v>
+        <v>4.043634177497424e-11</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.505134457299391e-10</v>
+        <v>5.205053055234998e-11</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.960560933715442e-09</v>
+        <v>3.284062952135791e-11</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.410242837593614e-09</v>
+        <v>8.536667032987832e-12</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.118989967352491e-08</v>
+        <v>2.87507795349029e-11</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.844192709654635e-08</v>
+        <v>9.504107223445857e-11</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.483710540157062e-09</v>
+        <v>7.486362918474043e-11</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.338059410637698e-09</v>
+        <v>8.385417360479153e-12</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.987502384892537e-09</v>
+        <v>7.939368606990627e-11</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.02295957762999e-09</v>
+        <v>1.031059092271303e-11</v>
       </c>
       <c r="AK12" t="n">
-        <v>5.423371973733992e-09</v>
+        <v>7.902175441776293e-12</v>
       </c>
       <c r="AL12" t="n">
-        <v>9.254801369706911e-09</v>
+        <v>2.345345792575948e-11</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.602716848125851e-10</v>
+        <v>2.309694623059411e-11</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.24930704564963e-09</v>
+        <v>1.127479533347131e-11</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.871978350109771e-09</v>
+        <v>5.028834987319541e-11</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.700260707897087e-09</v>
+        <v>3.769098921857506e-11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.984490484920116e-09</v>
+        <v>1.729995313670685e-11</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.226086674525732e-09</v>
+        <v>4.425019378695438e-14</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.991682871022476e-09</v>
+        <v>2.306517823957854e-11</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.370145718051276e-09</v>
+        <v>1.249654893453744e-12</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.226127904236819e-08</v>
+        <v>2.485337491364703e-10</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.922145192485459e-09</v>
+        <v>1.756184260515159e-11</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.116779805940496e-08</v>
+        <v>1.167250063965897e-11</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.022667780631764e-09</v>
+        <v>9.396413508389045e-11</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.231245018919253e-09</v>
+        <v>2.411619515196861e-11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.69299044070226e-09</v>
+        <v>1.05308418235639e-11</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.931414387954192e-09</v>
+        <v>3.791451874679552e-11</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.51955088512068e-08</v>
+        <v>2.13798423409628e-11</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.221332534053545e-09</v>
+        <v>1.617954902000118e-11</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.126952444342805e-10</v>
+        <v>5.130892932747599e-11</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.406036951427495e-09</v>
+        <v>4.094606945170831e-11</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.562361765105607e-09</v>
+        <v>3.535088888284577e-11</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.94665066288735e-08</v>
+        <v>1.434953718348897e-11</v>
       </c>
       <c r="BH12" t="n">
-        <v>6.572584698716355e-09</v>
+        <v>1.199111122895946e-12</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.807301508449655e-08</v>
+        <v>7.311192450065729e-12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>2.607230698004059e-08</v>
+        <v>8.473325513458363e-11</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.846137465122411e-09</v>
+        <v>2.603320337080106e-11</v>
       </c>
       <c r="BL12" t="n">
-        <v>2.085216443958871e-10</v>
+        <v>8.952324125066635e-12</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.85557305631967e-10</v>
+        <v>9.421226992989418e-11</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.395721671570982e-08</v>
+        <v>7.929822597174674e-12</v>
       </c>
       <c r="BO12" t="n">
-        <v>6.713088307463977e-09</v>
+        <v>1.025046540703567e-11</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.397110314220299e-09</v>
+        <v>1.010246331034637e-10</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.254833984087327e-09</v>
+        <v>3.223502714755355e-11</v>
       </c>
       <c r="BR12" t="n">
-        <v>8.694394537656081e-09</v>
+        <v>5.09939833415185e-11</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.440539243446892e-09</v>
+        <v>4.168848252716906e-11</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.241270363218973e-09</v>
+        <v>9.910404961954722e-12</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.652796370407941e-09</v>
+        <v>1.372858771109264e-11</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.325841925137183e-08</v>
+        <v>1.479930067382895e-10</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.877462320810992e-09</v>
+        <v>6.960850298942667e-12</v>
       </c>
       <c r="BX12" t="n">
-        <v>1.707161167985305e-08</v>
+        <v>3.992443875500129e-11</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.117208903167466e-08</v>
+        <v>4.320683394398728e-11</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.802139104611911e-09</v>
+        <v>2.329598666750421e-11</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.039499863964011e-08</v>
+        <v>5.921621526461252e-11</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.295003463994362e-09</v>
+        <v>3.307590659695769e-11</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.113488590220868e-08</v>
+        <v>3.904421924660895e-11</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.182063306767958e-10</v>
+        <v>1.495503894333172e-11</v>
       </c>
       <c r="CE12" t="n">
-        <v>7.139281610335502e-09</v>
+        <v>6.113255041073629e-11</v>
       </c>
       <c r="CF12" t="n">
-        <v>9.629346209294454e-09</v>
+        <v>2.352844048064684e-12</v>
       </c>
       <c r="CG12" t="n">
-        <v>8.86292550461576e-09</v>
+        <v>3.120906311160354e-12</v>
       </c>
       <c r="CH12" t="n">
-        <v>4.044317769569261e-09</v>
+        <v>5.007527378864118e-11</v>
       </c>
       <c r="CI12" t="n">
-        <v>3.370802525992644e-10</v>
+        <v>7.414490896251458e-12</v>
       </c>
       <c r="CJ12" t="n">
-        <v>6.482820502640152e-09</v>
+        <v>1.642176845895182e-12</v>
       </c>
       <c r="CK12" t="n">
-        <v>3.018583605296499e-09</v>
+        <v>1.571985250303776e-11</v>
       </c>
       <c r="CL12" t="n">
-        <v>7.952315250747688e-09</v>
+        <v>2.040990987328684e-11</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.34346951341513e-08</v>
+        <v>5.951354686839494e-11</v>
       </c>
       <c r="CN12" t="n">
-        <v>9.87972192945108e-09</v>
+        <v>1.544585015444966e-10</v>
       </c>
       <c r="CO12" t="n">
-        <v>2.24169260931717e-09</v>
+        <v>4.941021203297424e-11</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.531935645004978e-08</v>
+        <v>2.282296227007485e-11</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.342773252119514e-09</v>
+        <v>2.183125555332843e-11</v>
       </c>
       <c r="CR12" t="n">
-        <v>6.802157503926765e-09</v>
+        <v>4.906421102734981e-11</v>
       </c>
       <c r="CS12" t="n">
-        <v>6.281399400620558e-09</v>
+        <v>3.39465608401035e-11</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.491550077365901e-08</v>
+        <v>3.829387328069256e-12</v>
       </c>
       <c r="CU12" t="n">
-        <v>8.578183496865677e-09</v>
+        <v>3.127683181891605e-11</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.386718045421787e-10</v>
+        <v>5.432232788593616e-12</v>
       </c>
       <c r="CW12" t="n">
-        <v>6.596579726902974e-09</v>
+        <v>5.906302530389596e-11</v>
       </c>
       <c r="CX12" t="n">
-        <v>8.288521868848875e-09</v>
+        <v>8.614140650786695e-12</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.440154218101952e-08</v>
+        <v>1.869213464567032e-11</v>
       </c>
       <c r="CZ12" t="n">
-        <v>5.497023281009206e-09</v>
+        <v>3.827291608637928e-11</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.228731338898115e-09</v>
+        <v>4.45779697877402e-12</v>
       </c>
       <c r="DB12" t="n">
-        <v>5.350624388000824e-09</v>
+        <v>8.562263745237608e-12</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.659299974145824e-09</v>
+        <v>2.148647058886066e-11</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.183333400855417e-09</v>
+        <v>2.918161892684346e-11</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.0775014658293e-08</v>
+        <v>2.499933766941798e-11</v>
       </c>
       <c r="DF12" t="n">
-        <v>5.474358744095298e-09</v>
+        <v>2.144481120458508e-11</v>
       </c>
       <c r="DG12" t="n">
-        <v>8.168307807920883e-09</v>
+        <v>6.073914808613079e-12</v>
       </c>
       <c r="DH12" t="n">
-        <v>5.369560440726673e-08</v>
+        <v>2.555860904862595e-11</v>
       </c>
       <c r="DI12" t="n">
-        <v>2.995139780637146e-08</v>
+        <v>1.805576695101951e-11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>8.205033097397063e-09</v>
+        <v>2.482998529007574e-11</v>
       </c>
       <c r="DK12" t="n">
-        <v>1.393804005545007e-08</v>
+        <v>2.983358352026677e-11</v>
       </c>
       <c r="DL12" t="n">
-        <v>2.89194961311523e-08</v>
+        <v>6.09169867327175e-11</v>
       </c>
       <c r="DM12" t="n">
-        <v>1.766388590951351e-09</v>
+        <v>2.382604530337673e-11</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.29153487904432e-09</v>
+        <v>7.307071614448546e-12</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.370989265505386e-09</v>
+        <v>2.48873231051272e-11</v>
       </c>
       <c r="DP12" t="n">
-        <v>1.252496417691873e-08</v>
+        <v>9.443295104216709e-12</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.518084904096668e-09</v>
+        <v>4.585188478900548e-11</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.479363960451792e-09</v>
+        <v>2.3544929027286e-12</v>
       </c>
       <c r="DS12" t="n">
-        <v>6.597256074769575e-09</v>
+        <v>5.081582377108873e-11</v>
       </c>
       <c r="DT12" t="n">
-        <v>2.673178567391687e-09</v>
+        <v>1.497684615214823e-11</v>
       </c>
       <c r="DU12" t="n">
-        <v>9.999179262365487e-11</v>
+        <v>1.270906470340893e-11</v>
       </c>
       <c r="DV12" t="n">
-        <v>1.227029944317337e-08</v>
+        <v>1.453355404773538e-11</v>
       </c>
       <c r="DW12" t="n">
-        <v>5.42514144719064e-10</v>
+        <v>5.715799361594165e-12</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.500385415909022e-08</v>
+        <v>6.29725993572805e-11</v>
       </c>
       <c r="DY12" t="n">
-        <v>1.058895993111264e-08</v>
+        <v>1.638578508988964e-11</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.118709456297665e-09</v>
+        <v>2.286554626196313e-11</v>
       </c>
       <c r="EA12" t="n">
-        <v>1.933927862296514e-08</v>
+        <v>1.294519630379298e-10</v>
       </c>
       <c r="EB12" t="n">
-        <v>9.909178366740434e-09</v>
+        <v>9.687611823849807e-12</v>
       </c>
       <c r="EC12" t="n">
-        <v>5.801278346595495e-10</v>
+        <v>1.236293359352381e-11</v>
       </c>
       <c r="ED12" t="n">
-        <v>6.617701053812652e-09</v>
+        <v>8.091806391608003e-11</v>
       </c>
       <c r="EE12" t="n">
-        <v>3.822097749406339e-09</v>
+        <v>6.961052567699966e-11</v>
       </c>
       <c r="EF12" t="n">
-        <v>2.251196562497171e-09</v>
+        <v>2.505303603461684e-11</v>
       </c>
       <c r="EG12" t="n">
-        <v>2.544841004592513e-09</v>
+        <v>2.354019756900527e-14</v>
       </c>
       <c r="EH12" t="n">
-        <v>7.555390091340541e-09</v>
+        <v>7.805081234102396e-12</v>
       </c>
       <c r="EI12" t="n">
-        <v>1.087370460339798e-08</v>
+        <v>4.218028010205543e-11</v>
       </c>
       <c r="EJ12" t="n">
-        <v>8.172563958908086e-09</v>
+        <v>8.787821165201493e-12</v>
       </c>
       <c r="EK12" t="n">
-        <v>1.192217990997335e-09</v>
+        <v>1.795115445180073e-11</v>
       </c>
       <c r="EL12" t="n">
-        <v>1.044157293961234e-08</v>
+        <v>1.271077340603277e-11</v>
       </c>
       <c r="EM12" t="n">
-        <v>5.232945188282656e-09</v>
+        <v>1.885312739258183e-11</v>
       </c>
       <c r="EN12" t="n">
-        <v>3.101655376980261e-09</v>
+        <v>4.682025600555306e-11</v>
       </c>
       <c r="EO12" t="n">
-        <v>1.929155502011781e-09</v>
+        <v>8.439456598841044e-12</v>
       </c>
       <c r="EP12" t="n">
-        <v>1.520265469068249e-09</v>
+        <v>3.520765276543436e-11</v>
       </c>
       <c r="EQ12" t="n">
-        <v>8.930964412456888e-09</v>
+        <v>3.272599205517146e-12</v>
       </c>
       <c r="ER12" t="n">
-        <v>5.219948917556394e-09</v>
+        <v>8.742772131253851e-13</v>
       </c>
       <c r="ES12" t="n">
-        <v>3.109011714741428e-08</v>
+        <v>1.703530025376487e-11</v>
       </c>
       <c r="ET12" t="n">
-        <v>1.414827033308086e-09</v>
+        <v>1.603528247684505e-11</v>
       </c>
       <c r="EU12" t="n">
-        <v>5.294975569114513e-09</v>
+        <v>5.076024670036539e-12</v>
       </c>
       <c r="EV12" t="n">
-        <v>1.011757166935467e-08</v>
+        <v>3.370192319662735e-11</v>
       </c>
       <c r="EW12" t="n">
-        <v>1.214722655795697e-09</v>
+        <v>3.432656242585708e-11</v>
       </c>
       <c r="EX12" t="n">
-        <v>2.830510714701973e-09</v>
+        <v>1.141694811607197e-11</v>
       </c>
       <c r="EY12" t="n">
-        <v>7.140719571196996e-09</v>
+        <v>6.546845010557689e-11</v>
       </c>
       <c r="EZ12" t="n">
-        <v>9.15638143084152e-09</v>
+        <v>2.64464318500135e-12</v>
       </c>
       <c r="FA12" t="n">
-        <v>1.328063170547011e-08</v>
+        <v>1.261182651368653e-11</v>
       </c>
       <c r="FB12" t="n">
-        <v>3.746263299575503e-09</v>
+        <v>3.069035650615781e-11</v>
       </c>
       <c r="FC12" t="n">
-        <v>1.798065030200746e-09</v>
+        <v>9.218875662853065e-12</v>
       </c>
       <c r="FD12" t="n">
-        <v>6.368741090057028e-09</v>
+        <v>8.822940641972643e-12</v>
       </c>
       <c r="FE12" t="n">
-        <v>3.892149713635717e-09</v>
+        <v>2.343870063314935e-11</v>
       </c>
       <c r="FF12" t="n">
-        <v>8.831781528328975e-09</v>
+        <v>3.4305554924563e-11</v>
       </c>
       <c r="FG12" t="n">
-        <v>3.76081027431141e-10</v>
+        <v>1.9507773868499e-11</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.009874739388295e-09</v>
+        <v>4.223242415501982e-12</v>
       </c>
       <c r="FI12" t="n">
-        <v>1.477609945510494e-08</v>
+        <v>3.209028875961195e-11</v>
       </c>
       <c r="FJ12" t="n">
-        <v>2.580113012129459e-08</v>
+        <v>6.118534845445112e-11</v>
       </c>
       <c r="FK12" t="n">
-        <v>6.542795194519613e-09</v>
+        <v>4.085156692090752e-12</v>
       </c>
       <c r="FL12" t="n">
-        <v>1.327971732578703e-09</v>
+        <v>4.646120294049538e-11</v>
       </c>
       <c r="FM12" t="n">
-        <v>1.06169784075405e-08</v>
+        <v>2.117775746435235e-11</v>
       </c>
       <c r="FN12" t="n">
-        <v>3.599592846015298e-09</v>
+        <v>4.128024311267353e-11</v>
       </c>
       <c r="FO12" t="n">
-        <v>7.479459718240378e-09</v>
+        <v>4.780657120173615e-11</v>
       </c>
       <c r="FP12" t="n">
-        <v>1.270426430721727e-08</v>
+        <v>3.481789162540494e-11</v>
       </c>
       <c r="FQ12" t="n">
-        <v>5.230844202230855e-09</v>
+        <v>4.356582455899982e-11</v>
       </c>
       <c r="FR12" t="n">
-        <v>2.710940139039053e-09</v>
+        <v>2.026648987518698e-11</v>
       </c>
       <c r="FS12" t="n">
-        <v>4.70063321600378e-10</v>
+        <v>5.263366478769349e-11</v>
       </c>
       <c r="FT12" t="n">
-        <v>2.315757186011069e-08</v>
+        <v>5.717610412903085e-11</v>
       </c>
       <c r="FU12" t="n">
-        <v>2.829166678708361e-09</v>
+        <v>5.899870869630064e-11</v>
       </c>
       <c r="FV12" t="n">
-        <v>4.814568743682912e-09</v>
+        <v>1.974402412396881e-11</v>
       </c>
       <c r="FW12" t="n">
-        <v>7.694433534766176e-09</v>
+        <v>5.427375215916186e-11</v>
       </c>
       <c r="FX12" t="n">
-        <v>9.062694594774712e-09</v>
+        <v>8.813870640278498e-12</v>
       </c>
       <c r="FY12" t="n">
-        <v>1.40075799848205e-08</v>
+        <v>1.384645176294441e-11</v>
       </c>
       <c r="FZ12" t="n">
-        <v>2.987786906771817e-09</v>
+        <v>1.93492652456051e-11</v>
       </c>
       <c r="GA12" t="n">
-        <v>1.510230718260175e-09</v>
+        <v>1.766998006247356e-11</v>
       </c>
       <c r="GB12" t="n">
-        <v>2.844847468708167e-09</v>
+        <v>4.671654556254179e-12</v>
       </c>
       <c r="GC12" t="n">
-        <v>9.19044396141544e-09</v>
+        <v>6.567408422641918e-11</v>
       </c>
       <c r="GD12" t="n">
-        <v>8.911069104833302e-10</v>
+        <v>5.291695900910831e-11</v>
       </c>
       <c r="GE12" t="n">
-        <v>3.209366639111977e-08</v>
+        <v>6.542497099637501e-11</v>
       </c>
       <c r="GF12" t="n">
-        <v>3.219865485348805e-09</v>
+        <v>3.714822720268796e-12</v>
       </c>
       <c r="GG12" t="n">
-        <v>7.910312405101649e-09</v>
+        <v>3.562927730627052e-11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.001459026359952986</v>
+        <v>2.263146416225936e-05</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008742037229239941</v>
+        <v>7.360192103078589e-05</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0003348226600792259</v>
+        <v>1.198150948766852e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005473760422319174</v>
+        <v>3.343345724715618e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001571685774251819</v>
+        <v>9.298598888562992e-05</v>
       </c>
       <c r="F13" t="n">
-        <v>0.005747264716774225</v>
+        <v>5.004692138754763e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005083561991341412</v>
+        <v>9.531152500130702e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008790353313088417</v>
+        <v>4.926045949105173e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>7.887050742283463e-05</v>
+        <v>9.725532436277717e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002175393979996443</v>
+        <v>7.424117939081043e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0.006013237871229649</v>
+        <v>0.0001749167713569477</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000558971893042326</v>
+        <v>1.487458484916715e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00566280260682106</v>
+        <v>6.535168358823285e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002775677479803562</v>
+        <v>0.0001047973200911656</v>
       </c>
       <c r="O13" t="n">
-        <v>0.007110401522368193</v>
+        <v>6.657614721916616e-05</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0006749879685230553</v>
+        <v>2.223024421255104e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001011195010505617</v>
+        <v>4.48858700110577e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0003093558480031788</v>
+        <v>2.452785702189431e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0006865454488433897</v>
+        <v>1.893011358333752e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001696872641332448</v>
+        <v>4.866692324867472e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0004904552479274571</v>
+        <v>2.044044322246918e-06</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001180798513814807</v>
+        <v>2.298229264852125e-05</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0006174397422000766</v>
+        <v>4.269315468263812e-05</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0006640617502853274</v>
+        <v>7.454361821146449e-07</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0009676753543317318</v>
+        <v>1.103955582948402e-05</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0002300317864865065</v>
+        <v>3.059238952118903e-05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0008187981438823044</v>
+        <v>8.117794095596764e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003099828027188778</v>
+        <v>2.868563024094328e-05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.001601472496986389</v>
+        <v>1.879906631074846e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001405243237968534</v>
+        <v>9.364919151266804e-08</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0008341030334122479</v>
+        <v>1.471501218475169e-05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001147539122030139</v>
+        <v>5.243383930064738e-05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0008519617840647697</v>
+        <v>1.150183834397467e-06</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001501155085861683</v>
+        <v>3.889115032507107e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0005837776698172092</v>
+        <v>0.0001015571397147141</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07702799141407e-05</v>
+        <v>7.176620783866383e-06</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.001083905925042927</v>
+        <v>2.797746856231242e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.001296663889661431</v>
+        <v>1.581165633979253e-07</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.992113488493487e-05</v>
+        <v>1.658121163927717e-06</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0002506710588932037</v>
+        <v>3.285920683993027e-06</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0003541757178027183</v>
+        <v>1.733672434056643e-05</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.001123963273130357</v>
+        <v>3.833396476693451e-06</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0008492937777191401</v>
+        <v>4.692734364653006e-06</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0002415463677607477</v>
+        <v>4.979762161383405e-05</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.001015267567709088</v>
+        <v>4.567893483908847e-06</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.001384896459057927</v>
+        <v>8.151412657753099e-06</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.007285944186151028</v>
+        <v>0.0001917455665534362</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0002054513897746801</v>
+        <v>1.148128649219871e-05</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0003832880174741149</v>
+        <v>2.987646075780503e-05</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0008896057261154056</v>
+        <v>7.496286707464606e-05</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.003052924759685993</v>
+        <v>5.17634252901189e-05</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0009052213281393051</v>
+        <v>1.136973241955275e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.002114600036293268</v>
+        <v>2.21690243051853e-06</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.001177160302177072</v>
+        <v>1.983806760108564e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0009729005396366119</v>
+        <v>4.71181956527289e-05</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.00130272947717458</v>
+        <v>5.128977500135079e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.002180631272494793</v>
+        <v>4.722963694803184e-06</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.002521147020161152</v>
+        <v>5.340551797416992e-05</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.003263534745201468</v>
+        <v>4.39342693425715e-05</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.002077704295516014</v>
+        <v>8.538486326870043e-06</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0001378958695568144</v>
+        <v>3.74413539248053e-05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002958555473014712</v>
+        <v>6.797751120757312e-05</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0001794115523807704</v>
+        <v>1.39520998345688e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001450149866286665</v>
+        <v>1.548164800624363e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.002251616446301341</v>
+        <v>4.868324322160333e-05</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0009743394330143929</v>
+        <v>1.703005364106502e-05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.002342659747228026</v>
+        <v>6.520184251712635e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.001914163818582892</v>
+        <v>5.955549204372801e-05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0006237959023565054</v>
+        <v>9.65297658694908e-07</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001482725027017295</v>
+        <v>2.017007500398904e-05</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0002225464413641021</v>
+        <v>4.830352918361314e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0006116752047091722</v>
+        <v>1.00625566119561e-05</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0007503945380449295</v>
+        <v>3.953465056838468e-05</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.003178100101649761</v>
+        <v>0.0001240326091647148</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.00085758714703843</v>
+        <v>1.146895829151617e-05</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0003119897446595132</v>
+        <v>3.110574471065775e-05</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0007952112937346101</v>
+        <v>3.669024590635672e-05</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0006135781877674162</v>
+        <v>1.757076097419485e-05</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.001445030909962952</v>
+        <v>1.738137325446587e-05</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.001200504368171096</v>
+        <v>7.468206604244187e-07</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0008070755284279585</v>
+        <v>1.855147274909541e-06</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0002015157806454226</v>
+        <v>5.656374924001284e-08</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.001657480839639902</v>
+        <v>2.973117625515442e-05</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0009607321117073298</v>
+        <v>7.673985237488523e-06</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.001203590538352728</v>
+        <v>7.224940418382175e-06</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0006387590547092259</v>
+        <v>1.698943378869444e-05</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.001010044477880001</v>
+        <v>1.44813502629404e-05</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002420321980025619</v>
+        <v>4.972494025423657e-06</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0001833169953897595</v>
+        <v>7.485734386136755e-06</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0004987985594198108</v>
+        <v>6.900698963363538e-07</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.001774107804521918</v>
+        <v>4.725402686744928e-05</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001215753611177206</v>
+        <v>9.41497492021881e-05</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0002220825845142826</v>
+        <v>2.039559149125125e-05</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001037910347804427</v>
+        <v>4.781706593348645e-05</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.000717730785254389</v>
+        <v>4.148860898567364e-05</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0003856830880977213</v>
+        <v>1.490315298724454e-06</v>
       </c>
       <c r="CS13" t="n">
-        <v>6.70876179356128e-05</v>
+        <v>1.470273673476186e-05</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0005580815486609936</v>
+        <v>3.886805643560365e-05</v>
       </c>
       <c r="CU13" t="n">
-        <v>9.044786565937102e-05</v>
+        <v>3.102766186202643e-06</v>
       </c>
       <c r="CV13" t="n">
-        <v>6.184025551192462e-05</v>
+        <v>1.013499604596291e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.001260031363926828</v>
+        <v>2.042448795691598e-05</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.001006324659101665</v>
+        <v>4.198805982014164e-06</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.001664659474045038</v>
+        <v>1.424016772944015e-05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0004385969368740916</v>
+        <v>1.760501254466362e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0009298402001149952</v>
+        <v>1.267927564185811e-05</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0004252430226188153</v>
+        <v>1.464949491492007e-05</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0008236184366978705</v>
+        <v>1.689150053607591e-06</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0002947594039142132</v>
+        <v>2.072119286822272e-06</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0008000225061550736</v>
+        <v>5.633283581119031e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.002894942183047533</v>
+        <v>3.06370020553004e-05</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0001242481521330774</v>
+        <v>2.762863550742622e-05</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.002611599862575531</v>
+        <v>2.656772085174453e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0007336454000324011</v>
+        <v>1.692664045549463e-05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0002064137806883082</v>
+        <v>2.327840775251389e-05</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.002349075628444552</v>
+        <v>2.058979043795262e-05</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0009692804887890816</v>
+        <v>5.884194251848385e-05</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0006387828034348786</v>
+        <v>9.617222531232983e-06</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0007887366809882224</v>
+        <v>5.398925168265123e-06</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0008881525136530399</v>
+        <v>1.569398045830894e-05</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.001038161804899573</v>
+        <v>3.343950083944947e-06</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.001265267143025994</v>
+        <v>1.252966285392176e-05</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0005441691027954221</v>
+        <v>2.556520485086367e-06</v>
       </c>
       <c r="DS13" t="n">
-        <v>9.756226791068912e-05</v>
+        <v>7.983797331689857e-06</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0001006184975267388</v>
+        <v>2.269014203193365e-06</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0001130683376686648</v>
+        <v>6.973260315135121e-05</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0006018509739078581</v>
+        <v>1.118462660087971e-05</v>
       </c>
       <c r="DW13" t="n">
-        <v>7.801281753927469e-05</v>
+        <v>1.26690110846539e-07</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.838083107941202e-06</v>
+        <v>8.447022992186248e-05</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.001588278682902455</v>
+        <v>9.242578016710468e-06</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0003917334834113717</v>
+        <v>1.545690975035541e-05</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.000728434941265732</v>
+        <v>6.750973261659965e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0001910044811666012</v>
+        <v>6.945721906959079e-06</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0004601605178322643</v>
+        <v>1.885886013042182e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0006169031257741153</v>
+        <v>1.917731970024761e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001023376826196909</v>
+        <v>2.375670737819746e-05</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0006153234280645847</v>
+        <v>3.531455877237022e-05</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0002174209366785362</v>
+        <v>2.799735375447199e-05</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.000415349641116336</v>
+        <v>3.714429112733342e-06</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0008526351302862167</v>
+        <v>1.979477383429185e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001319571165367961</v>
+        <v>1.356256052531535e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0006561340996995568</v>
+        <v>5.617776878352743e-06</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0007046983228065073</v>
+        <v>7.609564363519894e-06</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0002119667478837073</v>
+        <v>7.088121037668316e-06</v>
       </c>
       <c r="EN13" t="n">
-        <v>6.188057886902243e-05</v>
+        <v>6.725436833221465e-06</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0009413134539499879</v>
+        <v>3.296854993095621e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0003832058282569051</v>
+        <v>1.526984669908416e-05</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0008587978663854301</v>
+        <v>1.988937219721265e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.001015237532556057</v>
+        <v>2.299718744325219e-06</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.001024481374770403</v>
+        <v>7.947224366944283e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001704196794889867</v>
+        <v>8.710969268577173e-06</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0007967626443132758</v>
+        <v>2.08146793738706e-05</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.001062588300555944</v>
+        <v>9.032693014887627e-06</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0003707147261593491</v>
+        <v>5.078624326415593e-06</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001074893443728797</v>
+        <v>1.233682451129425e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.001106943702325225</v>
+        <v>3.626577745308168e-05</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0007030574488453567</v>
+        <v>5.876325303688645e-06</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001170658273622394</v>
+        <v>2.135924114554655e-05</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0005956157692708075</v>
+        <v>9.51711081143003e-06</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0009369153995066881</v>
+        <v>1.605775287316646e-05</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.000643597450107336</v>
+        <v>2.455348067087471e-07</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0003149733820464462</v>
+        <v>1.808111619538977e-06</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0007037165341898799</v>
+        <v>1.910187620524084e-06</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0007401420152746141</v>
+        <v>2.225332536909264e-05</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.001020566327497363</v>
+        <v>1.449460069125053e-05</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.001125936163589358</v>
+        <v>8.134828931360971e-06</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0003776111407205462</v>
+        <v>5.765384412370622e-05</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001949065772350878</v>
+        <v>3.968580131186172e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0006226543337106705</v>
+        <v>1.37841980176745e-05</v>
       </c>
       <c r="FM13" t="n">
-        <v>6.492732791230083e-05</v>
+        <v>1.370918016618816e-05</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0003504911146592349</v>
+        <v>5.024109486839734e-05</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0004030775453429669</v>
+        <v>1.741820233291946e-05</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001188623020425439</v>
+        <v>5.987158601783449e-06</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0002599877770990133</v>
+        <v>3.862555604428053e-05</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0001846035156631842</v>
+        <v>3.336570443934761e-05</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.001614946173503995</v>
+        <v>1.212249480886385e-05</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.00361947575584054</v>
+        <v>0.0002121492871083319</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001036434667184949</v>
+        <v>4.765392077388242e-06</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0005183673929423094</v>
+        <v>1.594581772224046e-05</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.001390791032463312</v>
+        <v>5.094794323667884e-05</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0001311347004957497</v>
+        <v>2.012359118452878e-06</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001168834627605975</v>
+        <v>1.217450790136354e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.001239452161826193</v>
+        <v>6.576812211278593e-06</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0004506417899392545</v>
+        <v>5.643352778861299e-06</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.001269000698812306</v>
+        <v>6.776511872885749e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0002110568748321384</v>
+        <v>6.385843335010577e-06</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0006211759755387902</v>
+        <v>3.496800218272256e-06</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.003395756473764777</v>
+        <v>7.780573469062801e-06</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.001827858155593276</v>
+        <v>4.097825512872078e-05</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0006794653600081801</v>
+        <v>1.803697705327068e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002952894428744912</v>
+        <v>0.0002173568936996162</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001287292689085007</v>
+        <v>0.0001112538011511788</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003663273993879557</v>
+        <v>0.0008701282204128802</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005996905267238617</v>
+        <v>0.0004228093021083623</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004169663297943771</v>
+        <v>9.457871783524752e-07</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0008323569782078266</v>
+        <v>0.00020674015104305</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0003869459615088999</v>
+        <v>5.455066275317222e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001795484218746424</v>
+        <v>0.0003116111911367625</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001388274133205414</v>
+        <v>0.0001449561677873135</v>
       </c>
       <c r="J14" t="n">
-        <v>0.003345927689224482</v>
+        <v>9.832189243752509e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0016211555339396</v>
+        <v>0.0001812293485272676</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002894103294238448</v>
+        <v>0.0007857571472413838</v>
       </c>
       <c r="M14" t="n">
-        <v>0.005516369827091694</v>
+        <v>0.0003391124191693962</v>
       </c>
       <c r="N14" t="n">
-        <v>0.002576034748926759</v>
+        <v>0.0002690519904717803</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0007505302201025188</v>
+        <v>0.0001910835417220369</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0008790172869339585</v>
+        <v>5.367257108446211e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.002455251291394234</v>
+        <v>0.0003444566100370139</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001102611422538757</v>
+        <v>5.728469113819301e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001630903338082135</v>
+        <v>1.63485856319312e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>4.42216478404589e-05</v>
+        <v>0.000101951343822293</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0003283145488239825</v>
+        <v>0.0001271370711037889</v>
       </c>
       <c r="V14" t="n">
-        <v>0.000462845986476168</v>
+        <v>0.0002489547769073397</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001220081700012088</v>
+        <v>3.980502879130654e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0003521289036143571</v>
+        <v>0.0002121478755725548</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0003396738320589066</v>
+        <v>6.878894782857969e-05</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.002097733085975051</v>
+        <v>6.002730515319854e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0002486348093952984</v>
+        <v>4.650702612707391e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.000207172823138535</v>
+        <v>2.426653372822329e-05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.001442840904928744</v>
+        <v>1.012177926895674e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0002826853597071022</v>
+        <v>0.0001812896080082282</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0006129546090960503</v>
+        <v>0.0001840324839577079</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0004918650956824422</v>
+        <v>0.0002159269351977855</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0002370245492784306</v>
+        <v>4.7382025513798e-05</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.04416015651077e-05</v>
+        <v>6.507226498797536e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0007610244792886078</v>
+        <v>0.0001348580844933167</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8.674986020196229e-05</v>
+        <v>6.695745105389506e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0002252768899779767</v>
+        <v>8.942025306168944e-05</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.001203810446895659</v>
+        <v>4.586242721416056e-05</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0005642549367621541</v>
+        <v>0.0001511125301476568</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0003930954844690859</v>
+        <v>0.0002220971218775958</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0002364858228247613</v>
+        <v>0.000102404854260385</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0003759610117413104</v>
+        <v>0.0002386726846452802</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001094706123694777</v>
+        <v>0.0001194393771584146</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0003245400148443878</v>
+        <v>4.83250041725114e-05</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0004390132962726057</v>
+        <v>1.529686596768443e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0002336686156922951</v>
+        <v>0.0001339839800493792</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0007470822893083096</v>
+        <v>6.623053923249245e-05</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.002157973125576973</v>
+        <v>0.0006566605879925191</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.004202811978757381</v>
+        <v>0.0004167931328993291</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0008585270261391997</v>
+        <v>0.0003762188134714961</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.001377644715830684</v>
+        <v>0.0003817791002802551</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.7859619371593e-05</v>
+        <v>0.0002862536057364196</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.002061840845271945</v>
+        <v>0.0001679053821135312</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.001117486273869872</v>
+        <v>1.030261410051025e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.003653157502412796</v>
+        <v>0.0003260137164033949</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0008838603971526027</v>
+        <v>7.641137926839292e-05</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0004624738357961178</v>
+        <v>4.038357292301953e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.001838446827605367</v>
+        <v>0.0004070799914188683</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.002171580446884036</v>
+        <v>0.0002670205431059003</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.603619552450255e-05</v>
+        <v>0.0003480457817204297</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.002150224288925529</v>
+        <v>0.0001615895016584545</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.004018281120806932</v>
+        <v>0.000137788854772225</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.000788514968007803</v>
+        <v>8.014276681933552e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0008149668574333191</v>
+        <v>4.549670120468363e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0007346394704654813</v>
+        <v>2.900836625485681e-05</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0008291468839161098</v>
+        <v>0.0001209221154567786</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0008628624491393566</v>
+        <v>2.040738036157563e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.002351075410842896</v>
+        <v>0.0002038597012870014</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0005153074744157493</v>
+        <v>0.0001150736934505403</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.001124458503909409</v>
+        <v>7.682975410716608e-05</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0006839531124569476</v>
+        <v>3.659390495158732e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.001238402328453958</v>
+        <v>5.351230356609449e-07</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001698524574749172</v>
+        <v>1.753533069859259e-06</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0009149276302196085</v>
+        <v>9.989873797167093e-05</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.001077530323527753</v>
+        <v>0.0003451874654274434</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.001882520969957113</v>
+        <v>0.0005985279567539692</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0004998702206648886</v>
+        <v>8.720874757273123e-05</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0001437826576875523</v>
+        <v>8.663203334435821e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0009580997284501791</v>
+        <v>0.0001720755244605243</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.002849032636731863</v>
+        <v>5.40159635420423e-06</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.001102098729461432</v>
+        <v>5.787134796264581e-06</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0004886806127615273</v>
+        <v>2.357894663873594e-05</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0007250792696140707</v>
+        <v>0.0001447795948479325</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0008624770562164485</v>
+        <v>0.0002033157652476802</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.001088200253434479</v>
+        <v>5.672697443515062e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0008167793275788426</v>
+        <v>3.272409594501369e-05</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0005220386665314436</v>
+        <v>3.19977061735699e-06</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0004928384441882372</v>
+        <v>6.010014658386353e-06</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0005732711288146675</v>
+        <v>3.95399474655278e-05</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.001127758645452559</v>
+        <v>1.320800220128149e-05</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.001146736554801464</v>
+        <v>5.025728023611009e-05</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.07702799141407e-05</v>
+        <v>0.0001950010773725808</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0002752459258772433</v>
+        <v>3.599423507694155e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.00106851221062243</v>
+        <v>0.000243777350988239</v>
       </c>
       <c r="CQ14" t="n">
-        <v>9.821490675676614e-05</v>
+        <v>0.0004096805932931602</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.001281336299143732</v>
+        <v>9.609907283447683e-05</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0008342140936292708</v>
+        <v>7.650449697393924e-05</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.00113436917308718</v>
+        <v>2.369256617384963e-05</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0004264558956492692</v>
+        <v>0.0001683480368228629</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0004449696862138808</v>
+        <v>5.936748493695632e-05</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0005475848447531462</v>
+        <v>5.037922528572381e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0004265112802386284</v>
+        <v>0.0001992682227864861</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0007320197182707489</v>
+        <v>6.709154695272446e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.000933758681640029</v>
+        <v>1.919129317684565e-06</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0005397568456828594</v>
+        <v>4.452443681657314e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002964804880321026</v>
+        <v>3.116361040156335e-05</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0002939938567578793</v>
+        <v>2.416547431494109e-05</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.001239472068846226</v>
+        <v>2.271835182909854e-05</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0007391230901703238</v>
+        <v>2.151008084183559e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.003490400034934282</v>
+        <v>0.0001216242089867592</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0004142616526223719</v>
+        <v>0.0005364040262065828</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.001513132825493813</v>
+        <v>0.000154423454659991</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0003498401783872396</v>
+        <v>0.0003094480198342353</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.001560721313580871</v>
+        <v>8.887816511560231e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.003897232236340642</v>
+        <v>0.0001973506005015224</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0001886927784653381</v>
+        <v>0.0001056270411936566</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0002797812921926379</v>
+        <v>7.639581599505618e-05</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.000429818406701088</v>
+        <v>0.0001090468867914751</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.000574880454223603</v>
+        <v>1.943367533385754e-05</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.001178172416985035</v>
+        <v>2.54551341640763e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>4.306211485527456e-05</v>
+        <v>3.632685547927395e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.001495757373049855</v>
+        <v>0.0001433386350981891</v>
       </c>
       <c r="DS14" t="n">
-        <v>7.417947927024215e-05</v>
+        <v>5.422525282483548e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>2.456112997606397e-05</v>
+        <v>0.000171176390722394</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0008428568253293633</v>
+        <v>3.833186201518402e-05</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0009339459938928485</v>
+        <v>0.0001050798091455363</v>
       </c>
       <c r="DW14" t="n">
-        <v>2.199919254053384e-05</v>
+        <v>0.0001434142322978005</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001127391660702415</v>
+        <v>9.952749678632244e-05</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0003093142877332866</v>
+        <v>3.59294208465144e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0008569161873310804</v>
+        <v>0.0001456771860830486</v>
       </c>
       <c r="EA14" t="n">
-        <v>7.749204814899713e-05</v>
+        <v>0.0001112176396418363</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0009976790752261877</v>
+        <v>0.000234165825531818</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0005159408319741488</v>
+        <v>0.0001371625694446266</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.001342947361990809</v>
+        <v>3.063990880036727e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>8.875296043697745e-05</v>
+        <v>2.059372855001129e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0004086128901690245</v>
+        <v>2.059293183265254e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.001169957336969674</v>
+        <v>4.765894118463621e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0008448881562799215</v>
+        <v>0.0001412730489391834</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.001446821494027972</v>
+        <v>3.869889042107388e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>4.630850162357092e-05</v>
+        <v>0.000124460319057107</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0004139896773267537</v>
+        <v>3.117137748631649e-05</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0002699406468309462</v>
+        <v>3.245582774979994e-05</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0006420720601454377</v>
+        <v>7.322770397877321e-05</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.001601869822479784</v>
+        <v>2.770684477582108e-05</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0006514196284115314</v>
+        <v>6.333850615192205e-05</v>
       </c>
       <c r="EP14" t="n">
-        <v>3.256873606005684e-05</v>
+        <v>0.0001374031126033515</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0007332839304581285</v>
+        <v>5.069305916549638e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.000389234017347917</v>
+        <v>0.0001190808980027214</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0007177666993811727</v>
+        <v>5.322575816535391e-05</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0003217046614736319</v>
+        <v>0.0002023028209805489</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0002392954047536477</v>
+        <v>3.090087557211518e-05</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.00254462007433176</v>
+        <v>0.0001504523388575763</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.001639742171391845</v>
+        <v>2.36096529988572e-05</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0003379270201548934</v>
+        <v>3.326184014440514e-05</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0007012705318629742</v>
+        <v>0.0001545806881040335</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0006229407736100256</v>
+        <v>0.0001965152914635837</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0009149792604148388</v>
+        <v>6.041012238711119e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.000821949215605855</v>
+        <v>5.14292605657829e-06</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0007187972078099847</v>
+        <v>6.830763595644385e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001525864354334772</v>
+        <v>3.31258270307444e-05</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0003256584168411791</v>
+        <v>9.849150956142694e-06</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.001339276088401675</v>
+        <v>1.002975295705255e-05</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0003116959123872221</v>
+        <v>3.743988054338843e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>6.175946327857673e-05</v>
+        <v>3.210202339687385e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0002041520638158545</v>
+        <v>0.0003064130723942071</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.00112973153591156</v>
+        <v>0.0001454619050491601</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.000515833031386137</v>
+        <v>0.0002860883250832558</v>
       </c>
       <c r="FL14" t="n">
-        <v>1.067123957909644e-05</v>
+        <v>0.0002157964918296784</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0004798914305865765</v>
+        <v>5.321144635672681e-05</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0003066303324885666</v>
+        <v>9.095781570067629e-05</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.000941219856031239</v>
+        <v>8.288538083434105e-05</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.001323232194408774</v>
+        <v>0.00024228505208157</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0009903509635478258</v>
+        <v>0.0001898247573990375</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.003035628003999591</v>
+        <v>0.000123709804029204</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.002454506466165185</v>
+        <v>0.00019262166460976</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001488256966695189</v>
+        <v>0.0001437017490388826</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.001543964026495814</v>
+        <v>0.0002378805656917393</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0003460198058746755</v>
+        <v>0.0002351035509491339</v>
       </c>
       <c r="FW14" t="n">
-        <v>2.627657158882357e-05</v>
+        <v>0.0002737459726631641</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.000953450333327055</v>
+        <v>0.0001987257710425183</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0003298080409877002</v>
+        <v>4.471396823646501e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.000689513748511672</v>
+        <v>0.0003277214709669352</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.001514266943559051</v>
+        <v>0.0002331684518139809</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0001383456692565233</v>
+        <v>0.0001077260822057724</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.001169565482996404</v>
+        <v>0.0001841301709646359</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.001675612293183804</v>
+        <v>9.386864985572174e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0005262935301288962</v>
+        <v>2.949174086097628e-05</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0005010132445022464</v>
+        <v>6.897444109199569e-06</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0006900894222781062</v>
+        <v>1.630786573514342e-05</v>
       </c>
     </row>
     <row r="15">
@@ -8965,2278 +8965,2278 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.002775745699182153</v>
+        <v>0.0004575295897666365</v>
       </c>
       <c r="B16" t="n">
-        <v>0.08466549962759018</v>
+        <v>0.003681439906358719</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008200023323297501</v>
+        <v>0.00027121277526021</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02781837061047554</v>
+        <v>9.66489315032959e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06213460862636566</v>
+        <v>0.000119516218546778</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0238741934299469</v>
+        <v>0.005847688764333725</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007895956747233868</v>
+        <v>0.0008047735318541527</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01233414560556412</v>
+        <v>0.001995096914470196</v>
       </c>
       <c r="I16" t="n">
-        <v>0.005917063914239407</v>
+        <v>0.0001249999040737748</v>
       </c>
       <c r="J16" t="n">
-        <v>0.003617201000452042</v>
+        <v>0.0009896634146571159</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06211022660136223</v>
+        <v>0.006061811465770006</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005519378930330276</v>
+        <v>0.0008525627781637013</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008929873816668987</v>
+        <v>0.0009118294692598283</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04887904599308968</v>
+        <v>0.001576096168719232</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02196934819221497</v>
+        <v>0.006193669978529215</v>
       </c>
       <c r="P16" t="n">
-        <v>0.00201257411390543</v>
+        <v>0.001188577269203961</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.006688475608825684</v>
+        <v>0.0008925041183829308</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0004900849889963865</v>
+        <v>0.001490486436523497</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0005754472222179174</v>
+        <v>6.502939504571259e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01299239229410887</v>
+        <v>0.000183930154889822</v>
       </c>
       <c r="U16" t="n">
-        <v>0.002174595138058066</v>
+        <v>0.0006586153758689761</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01172492746263742</v>
+        <v>0.001004290301352739</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0207443293184042</v>
+        <v>0.0006173592992126942</v>
       </c>
       <c r="X16" t="n">
-        <v>0.008568760007619858</v>
+        <v>0.0004699421697296202</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.005708609241992235</v>
+        <v>0.000336542958393693</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.01596545055508614</v>
+        <v>0.00024859030963853</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.001969293225556612</v>
+        <v>0.0002420709934085608</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.002487911842763424</v>
+        <v>0.001205996959470212</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.008609229698777199</v>
+        <v>0.0003889822110068053</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.001649179728701711</v>
+        <v>0.0002466290316078812</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.001220164238475263</v>
+        <v>0.0002708949614316225</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01151037309318781</v>
+        <v>0.001088702119886875</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0007564229890704155</v>
+        <v>0.002716157352551818</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.01172535587102175</v>
+        <v>0.0003559289907570928</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.002178769325837493</v>
+        <v>0.002851386787369847</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.001120883505791426</v>
+        <v>0.0006106774089857936</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.01332299411296844</v>
+        <v>7.018438191153109e-05</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0127282403409481</v>
+        <v>0.0004879445186816156</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.004804531112313271</v>
+        <v>0.00103801884688437</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.001687975600361824</v>
+        <v>0.0008841311791911721</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.009311525151133537</v>
+        <v>0.001565481070429087</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.01174545753747225</v>
+        <v>0.0005100428243167698</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.005169781390577555</v>
+        <v>0.0006597514729946852</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.001200385158881545</v>
+        <v>0.001302915974520147</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.005807708017528057</v>
+        <v>0.000232131642405875</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.008973131887614727</v>
+        <v>0.0008411856833845377</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.07423293590545654</v>
+        <v>0.005129524506628513</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.007945594377815723</v>
+        <v>0.00144130177795887</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.001829675631597638</v>
+        <v>0.001019054441712797</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.01606501638889313</v>
+        <v>0.001383003313094378</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.02748433127999306</v>
+        <v>0.004352646879851818</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.00822134967893362</v>
+        <v>0.0005610247026197612</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.01622993126511574</v>
+        <v>4.012233694083989e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.003203361062332988</v>
+        <v>0.000380824669264257</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.005933077074587345</v>
+        <v>7.806537178112194e-05</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.01808447577059269</v>
+        <v>0.000352794595528394</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0102428225800395</v>
+        <v>0.0006753687630407512</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.006028830539435148</v>
+        <v>0.001159447128884494</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0413934551179409</v>
+        <v>0.0003037932910956442</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.01062491536140442</v>
+        <v>0.0004482154035940766</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.00263238325715065</v>
+        <v>0.0002890681498683989</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.01698140799999237</v>
+        <v>0.001322071882896125</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.008385960012674332</v>
+        <v>0.0001289108186028898</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.01069763489067554</v>
+        <v>8.488439925713465e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03968445211648941</v>
+        <v>0.002975884824991226</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.009791621938347816</v>
+        <v>0.0002474074717611074</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.007984090596437454</v>
+        <v>0.0007412642007693648</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.01995229348540306</v>
+        <v>0.002021803520619869</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01001483760774136</v>
+        <v>0.001813490991480649</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.008972004055976868</v>
+        <v>0.002091811969876289</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.002496317028999329</v>
+        <v>0.0005360926152206957</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.002427368890494108</v>
+        <v>0.001795740565285087</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.007741217501461506</v>
+        <v>0.0004056431353092194</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.04135988652706146</v>
+        <v>0.002830113051459193</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.01823894493281841</v>
+        <v>0.0003283488040324301</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.002920077415183187</v>
+        <v>0.001328771119005978</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.01247169449925423</v>
+        <v>0.0001515425683464855</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.006376092322170734</v>
+        <v>0.001105104456655681</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.008364015258848667</v>
+        <v>0.0005793729214929044</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.003296392504125834</v>
+        <v>0.0006167072569951415</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0002362397499382496</v>
+        <v>0.0003480598097667098</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.003536507254466414</v>
+        <v>0.0001127396244555712</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.01375839114189148</v>
+        <v>0.001175425131805241</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.004398573655635118</v>
+        <v>3.415179889998399e-05</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.007188867311924696</v>
+        <v>8.621576125733554e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.005929180886596441</v>
+        <v>0.0002738687326200306</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.005121152848005295</v>
+        <v>0.001407376606948674</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.007432541809976101</v>
+        <v>0.0002288926771143451</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.002767586149275303</v>
+        <v>0.0006467654602602124</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.00206509162671864</v>
+        <v>0.0006710970774292946</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.02564477734267712</v>
+        <v>0.0007261410937644541</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.01884925179183483</v>
+        <v>0.002230682410299778</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.002832858823239803</v>
+        <v>0.001999812666326761</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.008324946276843548</v>
+        <v>0.0004472917353268713</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.009234917350113392</v>
+        <v>0.0002208358491770923</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.006995949894189835</v>
+        <v>0.0006678050267510116</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.005258374847471714</v>
+        <v>0.0008677648147568107</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.00525240134447813</v>
+        <v>0.0005565051687881351</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.005798657890409231</v>
+        <v>0.0008669804083183408</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.002734031993895769</v>
+        <v>0.0001519744982942939</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.009434906765818596</v>
+        <v>0.001091298880055547</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.005997347179800272</v>
+        <v>0.0003994863945990801</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.01195515692234039</v>
+        <v>0.0002069915062747896</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.003644029144197702</v>
+        <v>8.600542787462473e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.006592423655092716</v>
+        <v>0.001554627786390483</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.007157717831432819</v>
+        <v>0.000214075087569654</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.005294627044349909</v>
+        <v>0.0006231435108929873</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.0007760716835036874</v>
+        <v>0.0004805417265743017</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.003701833775267005</v>
+        <v>0.0005351070431061089</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.01767055690288544</v>
+        <v>0.001180886756628752</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.003464184002950788</v>
+        <v>0.0004620104446075857</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.04600765183568001</v>
+        <v>0.001033802866004407</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.01682198047637939</v>
+        <v>0.0008317026076838374</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.004556272644549608</v>
+        <v>0.0009399331756867468</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.01737227290868759</v>
+        <v>0.0001881588832475245</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.008253563195466995</v>
+        <v>0.001438036211766303</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.01086807996034622</v>
+        <v>0.001190927578136325</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.005872016306966543</v>
+        <v>0.001383038703352213</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.006437443662434816</v>
+        <v>0.0006842822767794132</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.01186506636440754</v>
+        <v>0.0007137497887015343</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.006085595116019249</v>
+        <v>0.002095639007166028</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.009693238884210587</v>
+        <v>0.000843077665194869</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.005061980336904526</v>
+        <v>0.0002635566052049398</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.002274144440889359</v>
+        <v>0.0002865722053684294</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.004332632292062044</v>
+        <v>0.0002647298679221421</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.001521008904092014</v>
+        <v>0.0007074488094076514</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.007803275249898434</v>
+        <v>0.0006005296600051224</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.003477447899058461</v>
+        <v>0.0006494474364444613</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.001006077160127461</v>
+        <v>0.0005602398887276649</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.007112016435712576</v>
+        <v>0.001104636350646615</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.004848198033869267</v>
+        <v>0.001003814162686467</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.001274796668440104</v>
+        <v>0.000523561961017549</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.005634766072034836</v>
+        <v>0.0002716860035434365</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.001009250991046429</v>
+        <v>0.0009091293904930353</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.002801819704473019</v>
+        <v>0.00128493329975754</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.004291790071874857</v>
+        <v>0.0005650715902447701</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.00639771344140172</v>
+        <v>0.0004916723119094968</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.00288782361894846</v>
+        <v>0.0007620671531185508</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.004758827853947878</v>
+        <v>0.001537256059236825</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.00659910636022687</v>
+        <v>0.0003398955159354955</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.001155969221144915</v>
+        <v>0.001309488783590496</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.007872195914387703</v>
+        <v>0.0004506534314714372</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.002582048997282982</v>
+        <v>0.000217791908653453</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.0004448805702850223</v>
+        <v>0.0001491721923230216</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.01229921728372574</v>
+        <v>0.0002908137394115329</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.003727988339960575</v>
+        <v>0.0001697963161859661</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.009644530713558197</v>
+        <v>0.001238471828401089</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.01205560471862555</v>
+        <v>0.0003665442927740514</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.0002467571757733822</v>
+        <v>0.001251027220860124</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.01433671358972788</v>
+        <v>0.000713891233317554</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.008070864714682102</v>
+        <v>0.0002049231698038056</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01028114464133978</v>
+        <v>0.0004100923251826316</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0009040943114086986</v>
+        <v>0.0001345996570307761</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.003278371645137668</v>
+        <v>3.079412272199988e-05</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.006790533661842346</v>
+        <v>0.001409686403349042</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.003262500511482358</v>
+        <v>0.0001058861817000434</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.008474231697618961</v>
+        <v>8.46887705847621e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.004515783861279488</v>
+        <v>8.337652980117127e-05</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.00778206018730998</v>
+        <v>0.001155615551397204</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.009986786171793938</v>
+        <v>0.0002434940106468275</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.003831059671938419</v>
+        <v>0.0005087090539745986</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.004873433150351048</v>
+        <v>4.665223968913779e-05</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0038249003700912</v>
+        <v>5.274196155369282e-07</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.009859996847808361</v>
+        <v>0.001384965609759092</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.006781581323593855</v>
+        <v>0.001175927580334246</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.01234133169054985</v>
+        <v>0.002150560962036252</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.005909998901188374</v>
+        <v>1.828768290579319e-06</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.002799382666125894</v>
+        <v>0.00150331761687994</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.00662772823125124</v>
+        <v>0.0005447337171062827</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.005427474156022072</v>
+        <v>0.001160115003585815</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.004777338821440935</v>
+        <v>0.00250410451553762</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.02156636491417885</v>
+        <v>8.58785497257486e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.003227892331779003</v>
+        <v>0.0006704095285385847</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.00719707366079092</v>
+        <v>0.00198855297639966</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.01654141955077648</v>
+        <v>4.917022306472063e-05</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.006625570356845856</v>
+        <v>0.0003861601580865681</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.004535953514277935</v>
+        <v>0.0006631193682551384</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.003882169490680099</v>
+        <v>0.0009030443616211414</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.002003559842705727</v>
+        <v>0.00327148986980319</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.003622429212555289</v>
+        <v>0.0007795458077453077</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0191524475812912</v>
+        <v>0.0002373768074903637</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.008121469989418983</v>
+        <v>5.436811261461116e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.001949854893609881</v>
+        <v>0.0006802896969020367</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.0008287064265459776</v>
+        <v>0.0004366734065115452</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.004431661684066057</v>
+        <v>0.002597271464765072</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.01017484813928604</v>
+        <v>0.001790489535778761</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.02285036444664001</v>
+        <v>0.0005677426815964282</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.002933511976152658</v>
+        <v>0.0002217437140643597</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.002873562974855304</v>
+        <v>0.0001287466293433681</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0009634827729314566</v>
+        <v>0.005210318136960268</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03095623292028904</v>
+        <v>0.04075130447745323</v>
       </c>
       <c r="C17" t="n">
-        <v>0.004767491016536951</v>
+        <v>0.001302883261814713</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02076093293726444</v>
+        <v>0.04005754739046097</v>
       </c>
       <c r="E17" t="n">
-        <v>0.006340131163597107</v>
+        <v>0.01690045185387135</v>
       </c>
       <c r="F17" t="n">
-        <v>0.002850731834769249</v>
+        <v>0.009760727174580097</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004853042773902416</v>
+        <v>0.02543041110038757</v>
       </c>
       <c r="H17" t="n">
-        <v>0.002923373598605394</v>
+        <v>0.01153149455785751</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000518529734108597</v>
+        <v>0.007219051010906696</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004754713736474514</v>
+        <v>0.005299613811075687</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0238961037248373</v>
+        <v>0.03713530674576759</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001098480774089694</v>
+        <v>0.002272626385092735</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0196125004440546</v>
+        <v>0.05213535577058792</v>
       </c>
       <c r="N17" t="n">
-        <v>0.009701753966510296</v>
+        <v>0.0293305478990078</v>
       </c>
       <c r="O17" t="n">
-        <v>0.007368166465312243</v>
+        <v>0.005328518338501453</v>
       </c>
       <c r="P17" t="n">
-        <v>0.002335539553314447</v>
+        <v>0.02242334559559822</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.002536564599722624</v>
+        <v>0.01105805393308401</v>
       </c>
       <c r="R17" t="n">
-        <v>0.002738645765930414</v>
+        <v>0.000934783136472106</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001658910885453224</v>
+        <v>0.00420632166787982</v>
       </c>
       <c r="T17" t="n">
-        <v>0.006075351964682341</v>
+        <v>0.01021319720894098</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0003237635537516326</v>
+        <v>0.006775315385311842</v>
       </c>
       <c r="V17" t="n">
-        <v>0.002401511883363128</v>
+        <v>0.005022038239985704</v>
       </c>
       <c r="W17" t="n">
-        <v>0.001469160779379308</v>
+        <v>0.009066758677363396</v>
       </c>
       <c r="X17" t="n">
-        <v>0.003773690201342106</v>
+        <v>0.0087540652602911</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.004116802476346493</v>
+        <v>0.003009119536727667</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.002271343721076846</v>
+        <v>0.007537996862083673</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0028212103061378</v>
+        <v>0.002713728230446577</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.002082329476252198</v>
+        <v>0.005250801332294941</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.005746162962168455</v>
+        <v>0.007500518579035997</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0006678241188637912</v>
+        <v>0.0001915683969855309</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0009274196345359087</v>
+        <v>0.01196817588061094</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0005436887731775641</v>
+        <v>0.01649145595729351</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0006144012440927327</v>
+        <v>0.01360980793833733</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.002543734619393945</v>
+        <v>0.004834096878767014</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.001247681444510818</v>
+        <v>0.003987401258200407</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.001255739713087678</v>
+        <v>0.007358905393630266</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.00239728600718081</v>
+        <v>0.002916384022682905</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.004202584270387888</v>
+        <v>0.01500219199806452</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0001473796437494457</v>
+        <v>0.003682836890220642</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.171793650835752e-05</v>
+        <v>0.0156390480697155</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.00216538505628705</v>
+        <v>0.0006451928056776524</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.002214817563071847</v>
+        <v>0.01030136086046696</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0029130051843822</v>
+        <v>0.005270152352750301</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.001988278003409505</v>
+        <v>0.00422095088288188</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.001274278271012008</v>
+        <v>0.001670862198807299</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.002393579576164484</v>
+        <v>0.0122529212385416</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.02198480069637299</v>
+        <v>0.03950601816177368</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0007659011171199381</v>
+        <v>0.002851803321391344</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.004813493229448795</v>
+        <v>0.01062022149562836</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0005546888569369912</v>
+        <v>0.0255636852234602</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0001770379021763802</v>
+        <v>0.0007632338092662394</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.003090352052822709</v>
+        <v>0.005635299254208803</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0005742307403124869</v>
+        <v>0.00475089717656374</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.879173214547336e-05</v>
+        <v>0.00479313638061285</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0007592361653223634</v>
+        <v>0.008035736158490181</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.005712345242500305</v>
+        <v>0.005521384999155998</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.007192236836999655</v>
+        <v>0.000106157036498189</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.005508816335350275</v>
+        <v>0.01082903333008289</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.009547584690153599</v>
+        <v>0.004534036386758089</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.002714326372370124</v>
+        <v>0.001985759707167745</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.002522217808291316</v>
+        <v>0.005959128029644489</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.002245937706902623</v>
+        <v>0.006842085160315037</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.001602682983502746</v>
+        <v>0.005490753334015608</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.003747092559933662</v>
+        <v>0.002380732912570238</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.004854531027376652</v>
+        <v>0.01017354521900415</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.00417048018425703</v>
+        <v>0.01014464721083641</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0002183036849601194</v>
+        <v>0.01142561249434948</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.003125813324004412</v>
+        <v>0.01705366931855679</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.002171340631321073</v>
+        <v>0.01150057185441256</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0005199360311962664</v>
+        <v>0.001473132986575365</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.001014398643746972</v>
+        <v>0.001098279375582933</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.001914883847348392</v>
+        <v>0.0007459883345291018</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.002217665314674377</v>
+        <v>0.01008013263344765</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.01124753337353468</v>
+        <v>0.03534986078739166</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.004768269136548042</v>
+        <v>0.004748128820210695</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.00438227690756321</v>
+        <v>0.01566823944449425</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.001008128747344017</v>
+        <v>0.008830343373119831</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.001883457764051855</v>
+        <v>0.01327764429152012</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.002518720924854279</v>
+        <v>0.008325490169227123</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.001378832967020571</v>
+        <v>0.0007652046624571085</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.002379244426265359</v>
+        <v>0.004522436298429966</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0007000517216511071</v>
+        <v>0.004238228313624859</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.005380258895456791</v>
+        <v>0.01006069406867027</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.002327275462448597</v>
+        <v>0.004175442270934582</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.002298614708706737</v>
+        <v>0.01684698835015297</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0009413972729817033</v>
+        <v>0.003584723686799407</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.001360255759209394</v>
+        <v>0.002386312698945403</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0008416950004175305</v>
+        <v>4.331342643126845e-05</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0004787161306012422</v>
+        <v>0.003176070749759674</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.00108646263834089</v>
+        <v>0.001163442037068307</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.006279961671680212</v>
+        <v>0.003200020175427198</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.003797858720645308</v>
+        <v>0.02211042679846287</v>
       </c>
       <c r="CO17" t="n">
-        <v>5.744173540733755e-05</v>
+        <v>0.003162588691338897</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.003629961516708136</v>
+        <v>0.02657655999064445</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.003107387106865644</v>
+        <v>0.01065164990723133</v>
       </c>
       <c r="CR17" t="n">
-        <v>8.868724398780614e-05</v>
+        <v>0.0001144623383879662</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.003255148185417056</v>
+        <v>0.007145186886191368</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.004983484745025635</v>
+        <v>0.0002682915364857763</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0002922233543358743</v>
+        <v>0.009397370740771294</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0005840958328917623</v>
+        <v>0.002362346276640892</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.004610638599842787</v>
+        <v>0.008198043331503868</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.002882303902879357</v>
+        <v>0.003015803173184395</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.003227602457627654</v>
+        <v>0.01713023707270622</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.001053949235938489</v>
+        <v>0.006223684176802635</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.002085766289383173</v>
+        <v>0.0005834382027387619</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0009579907055012882</v>
+        <v>0.0009732745820656419</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0008361720247194171</v>
+        <v>0.003312383312731981</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.0001805636566132307</v>
+        <v>0.0003086014476139098</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.002156747737899423</v>
+        <v>0.007109357044100761</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.004922848660498857</v>
+        <v>0.0215485692024231</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.001285048550926149</v>
+        <v>0.006240794435143471</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.007920424453914165</v>
+        <v>0.01526354439556599</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.000987403211183846</v>
+        <v>0.01077915448695421</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.002913266653195024</v>
+        <v>0.009215731173753738</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.002131512155756354</v>
+        <v>0.004467026330530643</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0005707127857021987</v>
+        <v>0.01817787624895573</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0004238483379594982</v>
+        <v>0.007418802939355373</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.094017690978944e-05</v>
+        <v>0.008274500258266926</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.001112251309677958</v>
+        <v>0.009081641212105751</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.001689888071268797</v>
+        <v>0.004835445433855057</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0005516272503882647</v>
+        <v>0.004042312502861023</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.00267862225882709</v>
+        <v>0.001688852440565825</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.002078042831271887</v>
+        <v>0.01080237701535225</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.001409653341397643</v>
+        <v>0.00310785393230617</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.002284752670675516</v>
+        <v>0.0099744638428092</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.003208696842193604</v>
+        <v>0.01825895346701145</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0001250948989763856</v>
+        <v>0.001390607096254826</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.002334000775590539</v>
+        <v>0.004646381363272667</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.00231657805852592</v>
+        <v>0.0002076323144137859</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.001986671006307006</v>
+        <v>0.00786264706403017</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.002583469729870558</v>
+        <v>0.001028506085276604</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0009428908815607429</v>
+        <v>0.0004100254736840725</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.001715774997137487</v>
+        <v>0.0008453471818938851</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0008802033262327313</v>
+        <v>0.01500297710299492</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.002278938191011548</v>
+        <v>0.008109143935143948</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0001083773095160723</v>
+        <v>0.001647498109377921</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.003094862448051572</v>
+        <v>0.01076307334005833</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.002478497801348567</v>
+        <v>0.00195500161498785</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.003398898988962173</v>
+        <v>0.01306954957544804</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.001551443827338517</v>
+        <v>0.006255751475691795</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.003473853226751089</v>
+        <v>8.836801862344146e-05</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0005827186978422105</v>
+        <v>0.001401942456141114</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0005123412702232599</v>
+        <v>0.002683937549591064</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0005428817821666598</v>
+        <v>0.001493116957135499</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0002390615409240127</v>
+        <v>0.002341967076063156</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.003888161387294531</v>
+        <v>0.006152060814201832</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.003659315640106797</v>
+        <v>0.0005428263684734702</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.001109404605813324</v>
+        <v>0.01273567974567413</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0004473461012821645</v>
+        <v>0.002294420963153243</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.001616314868442714</v>
+        <v>0.0001728495117276907</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.002060570055618882</v>
+        <v>0.00611617136746645</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.00293122953735292</v>
+        <v>0.005138498730957508</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0005695477011613548</v>
+        <v>0.009067352861166</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.0002506308956071734</v>
+        <v>0.004615026991814375</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.004927321337163448</v>
+        <v>0.01304031070321798</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.001935501582920551</v>
+        <v>0.00236059445887804</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.003351020393893123</v>
+        <v>0.01809614896774292</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0005340586649253964</v>
+        <v>0.003734452649950981</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.002097966847941279</v>
+        <v>0.004211564548313618</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.000990967033430934</v>
+        <v>0.001088415971025825</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.000400939752580598</v>
+        <v>0.003611617255955935</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.0008856009226292372</v>
+        <v>0.001316377078182995</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0006215579924173653</v>
+        <v>0.002289556199684739</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.001456131576560438</v>
+        <v>0.007305343635380268</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.002289841882884502</v>
+        <v>0.0006547804805450141</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.002589494455605745</v>
+        <v>0.01058728247880936</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.001635188818909228</v>
+        <v>0.004185098689049482</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.003427086398005486</v>
+        <v>0.00147154729347676</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.0003291055909357965</v>
+        <v>0.002732709050178528</v>
       </c>
       <c r="FN17" t="n">
-        <v>2.512703940737993e-05</v>
+        <v>0.002262087073177099</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0004514259635470808</v>
+        <v>0.008035341277718544</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0001843056525103748</v>
+        <v>0.00114499544724822</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.004236432258039713</v>
+        <v>0.006429335102438927</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.003304737387225032</v>
+        <v>0.003895367030054331</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.00274854339659214</v>
+        <v>0.007726942654699087</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0001579251402290538</v>
+        <v>0.01437825616449118</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.002834150101989508</v>
+        <v>0.004423027392476797</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.001375416992232203</v>
+        <v>0.009049322456121445</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.001257400377653539</v>
+        <v>0.01181851793080568</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0007269377820193768</v>
+        <v>0.003347135148942471</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.005040921270847321</v>
+        <v>0.01291066594421864</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0007201615953817964</v>
+        <v>0.01292381435632706</v>
       </c>
       <c r="GA17" t="n">
-        <v>4.654750955523923e-05</v>
+        <v>0.008393056690692902</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0008422655519098043</v>
+        <v>0.005397862289100885</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0008608857751823962</v>
+        <v>0.01435799896717072</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.003230905625969172</v>
+        <v>0.01099994219839573</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.01046725176274776</v>
+        <v>0.01240420807152987</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.001379145192913711</v>
+        <v>0.003489717375487089</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.002635803306475282</v>
+        <v>0.003063563490286469</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0001042949734255672</v>
+        <v>0.0003522891202010214</v>
       </c>
       <c r="B18" t="n">
-        <v>0.004555853083729744</v>
+        <v>0.001953005790710449</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0003151394776068628</v>
+        <v>0.002828361932188272</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001972925383597612</v>
+        <v>0.001211318536661565</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001533274189569056</v>
+        <v>0.001166056958027184</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003110782708972692</v>
+        <v>0.002947252709418535</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003574738511815667</v>
+        <v>0.0001045063036144711</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001086939009837806</v>
+        <v>0.001380838686600327</v>
       </c>
       <c r="I18" t="n">
-        <v>8.732381684239954e-05</v>
+        <v>0.0001236888638231903</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0006048438954167068</v>
+        <v>0.0007678437395952642</v>
       </c>
       <c r="K18" t="n">
-        <v>0.003657442983239889</v>
+        <v>0.004597957711666822</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0007469336269423366</v>
+        <v>0.002648808062076569</v>
       </c>
       <c r="M18" t="n">
-        <v>0.001729989540763199</v>
+        <v>0.001151018659584224</v>
       </c>
       <c r="N18" t="n">
-        <v>0.001709580654278398</v>
+        <v>0.00135575351305306</v>
       </c>
       <c r="O18" t="n">
-        <v>0.00385058531537652</v>
+        <v>0.003457200014963746</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0003967431548517197</v>
+        <v>0.001877588219940662</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0001591914333403111</v>
+        <v>0.001170965610072017</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0001876323076430708</v>
+        <v>0.0004701170255430043</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0004325495683588088</v>
+        <v>0.001246380852535367</v>
       </c>
       <c r="T18" t="n">
-        <v>0.001078130677342415</v>
+        <v>0.0001918127672979608</v>
       </c>
       <c r="U18" t="n">
-        <v>7.769803778501227e-05</v>
+        <v>0.0006059168954379857</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0006142717320472002</v>
+        <v>7.475745223928243e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>2.321692954865284e-05</v>
+        <v>0.0001926792465383187</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0004018604231532663</v>
+        <v>1.220718695549294e-05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0004481153446249664</v>
+        <v>0.0005686002550646663</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.029300619848073e-05</v>
+        <v>0.001751331961713731</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0004688716435339302</v>
+        <v>0.0006294698105193675</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0002368156565353274</v>
+        <v>0.002401451114565134</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0009749686578288674</v>
+        <v>0.0004386389628052711</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0006172250723466277</v>
+        <v>7.358044967986643e-06</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0006159718031994998</v>
+        <v>0.0007881895871832967</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0006299305241554976</v>
+        <v>0.001972587313503027</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0004685850581154227</v>
+        <v>0.0002197276335209608</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0008533115615136921</v>
+        <v>0.001052780775353312</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0001723206078168005</v>
+        <v>0.001126763643696904</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.0002098983532050624</v>
+        <v>0.0001441458007320762</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0008225434576161206</v>
+        <v>0.0005406101699918509</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0008938767714425921</v>
+        <v>0.001473368494771421</v>
       </c>
       <c r="AM18" t="n">
-        <v>8.847200660966337e-06</v>
+        <v>0.0001217954559251666</v>
       </c>
       <c r="AN18" t="n">
-        <v>7.012218702584505e-05</v>
+        <v>0.0009720074594952166</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.0002881226828321815</v>
+        <v>0.001712264376692474</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.000674980110488832</v>
+        <v>0.0001520290243206546</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.0003569404361769557</v>
+        <v>0.001031209947541356</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.0002117474796250463</v>
+        <v>0.001581728691235185</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.0005086947930976748</v>
+        <v>8.014404738787562e-05</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.0008754266309551895</v>
+        <v>0.0007301202858798206</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.003969460260123014</v>
+        <v>0.003255649004131556</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.0004983284161426127</v>
+        <v>0.0007244646549224854</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.0002248668461106718</v>
+        <v>0.0004725958860944957</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.0003138406900689006</v>
+        <v>0.0009891402442008257</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.002131101675331593</v>
+        <v>0.001910219667479396</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.0004791319952346385</v>
+        <v>0.0001434219011571258</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.001237121992744505</v>
+        <v>0.0003595797752495855</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.0007018299074843526</v>
+        <v>0.0002329248673049733</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.277226303704083e-05</v>
+        <v>0.0005715388106182218</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.0008338932530023158</v>
+        <v>0.001295647583901882</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.001438532839529216</v>
+        <v>0.001062818570062518</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.0008063983405008912</v>
+        <v>0.0002758308546617627</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.001345098600722849</v>
+        <v>0.0003070645034313202</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.001074815867468715</v>
+        <v>1.083446841221303e-05</v>
       </c>
       <c r="BI18" t="n">
-        <v>9.077624417841434e-05</v>
+        <v>0.0006476384587585926</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.001585878548212349</v>
+        <v>0.001442040549591184</v>
       </c>
       <c r="BK18" t="n">
-        <v>2.636798308230937e-05</v>
+        <v>0.0001809032692108303</v>
       </c>
       <c r="BL18" t="n">
-        <v>2.480228431522846e-06</v>
+        <v>0.0004350950475782156</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.001407853793352842</v>
+        <v>0.002199887996539474</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.0004726657643914223</v>
+        <v>0.0001437241153325886</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.0008418839424848557</v>
+        <v>0.001512187882326543</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.001314855762757361</v>
+        <v>0.00144254369661212</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.0007360256859101355</v>
+        <v>0.000691194727551192</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.0008244400378316641</v>
+        <v>0.0009253769530914724</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.0001045597164193168</v>
+        <v>0.0008126843022182584</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.0004105849657207727</v>
+        <v>0.0005788921844214201</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.0003909315855707973</v>
+        <v>0.000935317890252918</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.002047659363597631</v>
+        <v>0.001856405637226999</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.000420689582824707</v>
+        <v>0.0004033847944810987</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.0001637405075598508</v>
+        <v>0.0001864655641838908</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.0007444879156537354</v>
+        <v>0.000570950738620013</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.0004262942529749125</v>
+        <v>0.0002885538851842284</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.0008300890913233161</v>
+        <v>0.0004337014979682863</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.0006091040559113026</v>
+        <v>0.0005996680702082813</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.0004194851208012551</v>
+        <v>0.0004400580946821719</v>
       </c>
       <c r="CD18" t="n">
-        <v>0.0001258822157979012</v>
+        <v>0.0006734763737767935</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.000861865992192179</v>
+        <v>0.0003669829457066953</v>
       </c>
       <c r="CF18" t="n">
-        <v>0.0004921042709611356</v>
+        <v>0.0004381349426694214</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.0006003221496939659</v>
+        <v>0.0003182506188750267</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.0002359891950618476</v>
+        <v>0.0006721882382407784</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.0004921956569887698</v>
+        <v>0.001057682558894157</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.0001720316940918565</v>
+        <v>0.0003270839806646109</v>
       </c>
       <c r="CK18" t="n">
-        <v>0.0002466454752720892</v>
+        <v>0.0001886582467705011</v>
       </c>
       <c r="CL18" t="n">
-        <v>0.0002924026339314878</v>
+        <v>8.679649181431159e-05</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.001199610065668821</v>
+        <v>0.000435670604929328</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.001203192048706114</v>
+        <v>0.003136321902275085</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.000372684997273609</v>
+        <v>0.0004920688224956393</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.0001978397340280935</v>
+        <v>0.0007901797071099281</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0007584429695270956</v>
+        <v>0.0007306962506845593</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.0002714649890549481</v>
+        <v>0.0005481733242049813</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.0001778715522959828</v>
+        <v>0.0003272712929174304</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.0005754953599534929</v>
+        <v>0.0001554550835862756</v>
       </c>
       <c r="CU18" t="n">
-        <v>0.0001647676981519908</v>
+        <v>1.725537003949285e-05</v>
       </c>
       <c r="CV18" t="n">
-        <v>0.000166877347510308</v>
+        <v>0.0006103056366555393</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.000608077913057059</v>
+        <v>0.0004818248853553087</v>
       </c>
       <c r="CX18" t="n">
-        <v>0.0006012868834659457</v>
+        <v>0.0002291376586072147</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.0009131251135841012</v>
+        <v>0.0004361352184787393</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.0001713368110358715</v>
+        <v>0.0002444893470965326</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.000436058733612299</v>
+        <v>0.001142758643254638</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.0003046410565730184</v>
+        <v>4.548332071863115e-06</v>
       </c>
       <c r="DC18" t="n">
-        <v>0.0006227525882422924</v>
+        <v>0.0002769248676486313</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.000173482607351616</v>
+        <v>0.0001133697951445356</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.0001643362629693002</v>
+        <v>0.0008057900122366846</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.001643707510083914</v>
+        <v>0.0008309889235533774</v>
       </c>
       <c r="DG18" t="n">
-        <v>9.084413613891229e-05</v>
+        <v>0.0005990611389279366</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.002350336639210582</v>
+        <v>0.00211458676494658</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.0006111909169703722</v>
+        <v>0.001445949310436845</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.0001774223928805441</v>
+        <v>0.0009678264614194632</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.001291879219934344</v>
+        <v>0.0008989028283394873</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.0006485126214101911</v>
+        <v>0.0005459948442876339</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.0005110410274937749</v>
+        <v>0.0003959728055633605</v>
       </c>
       <c r="DN18" t="n">
-        <v>4.570510645862669e-05</v>
+        <v>0.0004236669628880918</v>
       </c>
       <c r="DO18" t="n">
-        <v>9.126379154622555e-05</v>
+        <v>0.000825000402983278</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.0006268812576308846</v>
+        <v>0.0001488900015829131</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.0002732457069214433</v>
+        <v>0.001506951870396733</v>
       </c>
       <c r="DR18" t="n">
-        <v>5.354480163077824e-05</v>
+        <v>0.001934667699970305</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.0001912467705551535</v>
+        <v>0.0006591484998352826</v>
       </c>
       <c r="DT18" t="n">
-        <v>2.035677789535839e-05</v>
+        <v>5.07597578689456e-05</v>
       </c>
       <c r="DU18" t="n">
-        <v>4.877860919805244e-05</v>
+        <v>0.001078651053830981</v>
       </c>
       <c r="DV18" t="n">
-        <v>0.0003123153001070023</v>
+        <v>0.0003276502538938075</v>
       </c>
       <c r="DW18" t="n">
-        <v>1.706914918031543e-05</v>
+        <v>0.0008425456471741199</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.0005122345755808055</v>
+        <v>0.0001863756333477795</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.0009370297193527222</v>
+        <v>0.001414251513779163</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.0004053717420902103</v>
+        <v>0.001358199049718678</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.0002430884924251586</v>
+        <v>0.0003212458977941424</v>
       </c>
       <c r="EB18" t="n">
-        <v>4.602273111231625e-05</v>
+        <v>0.00104824302252382</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.0002368242130614817</v>
+        <v>8.731563139008358e-05</v>
       </c>
       <c r="ED18" t="n">
-        <v>0.000202837327378802</v>
+        <v>0.0001669866178417578</v>
       </c>
       <c r="EE18" t="n">
-        <v>0.0003776458033826202</v>
+        <v>0.0007009960827417672</v>
       </c>
       <c r="EF18" t="n">
-        <v>0.0005998764536343515</v>
+        <v>0.0008647035574540496</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.0001081514419638552</v>
+        <v>0.0005579902208410203</v>
       </c>
       <c r="EH18" t="n">
-        <v>5.342745498637669e-05</v>
+        <v>0.0002776552282739431</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.0003663243260234594</v>
+        <v>0.0002301777858519927</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.0001398636377416551</v>
+        <v>0.0001827747619245201</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.0004278275300748646</v>
+        <v>0.001584609388373792</v>
       </c>
       <c r="EL18" t="n">
-        <v>0.000365124229574576</v>
+        <v>0.0004656597157008946</v>
       </c>
       <c r="EM18" t="n">
-        <v>2.306023452547379e-05</v>
+        <v>0.0005665375501848757</v>
       </c>
       <c r="EN18" t="n">
-        <v>8.923303539631888e-05</v>
+        <v>5.423877155408263e-05</v>
       </c>
       <c r="EO18" t="n">
-        <v>0.0002580625005066395</v>
+        <v>0.000718248076736927</v>
       </c>
       <c r="EP18" t="n">
-        <v>8.665469795232639e-05</v>
+        <v>0.0005133197410032153</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0.001034362008795142</v>
+        <v>0.0009726221323944628</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.0007003085920587182</v>
+        <v>0.001010270440019667</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.0004042347718495876</v>
+        <v>0.0006227522972039878</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.0005423358525149524</v>
+        <v>0.0002342654042877257</v>
       </c>
       <c r="EU18" t="n">
-        <v>0.0004559912777040154</v>
+        <v>0.000669035769533366</v>
       </c>
       <c r="EV18" t="n">
-        <v>0.0007431359263136983</v>
+        <v>0.0001544717379147187</v>
       </c>
       <c r="EW18" t="n">
-        <v>8.521630661562085e-06</v>
+        <v>0.0009466497576795518</v>
       </c>
       <c r="EX18" t="n">
-        <v>3.051701787626371e-05</v>
+        <v>0.0006553332204930484</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.0006031816592440009</v>
+        <v>0.0005506919114850461</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0.0004503144591581076</v>
+        <v>0.0003968869859818369</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.0005004575359635055</v>
+        <v>0.0001520153600722551</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.0002642146137077361</v>
+        <v>0.0002775182656478137</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.000505151110701263</v>
+        <v>0.0009029466891661286</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.0003984836221206933</v>
+        <v>0.0003119647153653204</v>
       </c>
       <c r="FE18" t="n">
-        <v>0.0002910465118475258</v>
+        <v>9.177498577628285e-05</v>
       </c>
       <c r="FF18" t="n">
-        <v>0.0003572538553271443</v>
+        <v>0.0001374277053400874</v>
       </c>
       <c r="FG18" t="n">
-        <v>0.0002799121721182019</v>
+        <v>0.0002217950241174549</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.000464446929981932</v>
+        <v>0.0009607931133359671</v>
       </c>
       <c r="FI18" t="n">
-        <v>0.00104751274921</v>
+        <v>3.836296673398465e-05</v>
       </c>
       <c r="FJ18" t="n">
-        <v>7.353673572652042e-05</v>
+        <v>0.00196024333126843</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.0001547051360830665</v>
+        <v>0.0001873314613476396</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.0002502446877770126</v>
+        <v>0.0003387626493349671</v>
       </c>
       <c r="FM18" t="n">
-        <v>0.0002105574239976704</v>
+        <v>0.0008706764783710241</v>
       </c>
       <c r="FN18" t="n">
-        <v>5.286092709866352e-05</v>
+        <v>0.0004706328618340194</v>
       </c>
       <c r="FO18" t="n">
-        <v>6.254469190025702e-05</v>
+        <v>0.0003806075255852193</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.0003543436178006232</v>
+        <v>0.0003318069211672992</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.0005213869153521955</v>
+        <v>0.0008354480378329754</v>
       </c>
       <c r="FR18" t="n">
-        <v>0.0005253022536635399</v>
+        <v>0.000107649844721891</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.0005888078012503684</v>
+        <v>0.0004587335279211402</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.001145383343100548</v>
+        <v>0.0002956491953227669</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.0005565499886870384</v>
+        <v>0.00142122944816947</v>
       </c>
       <c r="FV18" t="n">
-        <v>0.0003435852704569697</v>
+        <v>0.0002867443254217505</v>
       </c>
       <c r="FW18" t="n">
-        <v>0.0008933815988712013</v>
+        <v>0.001045381650328636</v>
       </c>
       <c r="FX18" t="n">
-        <v>0.0001714074605843052</v>
+        <v>0.0005870225140824914</v>
       </c>
       <c r="FY18" t="n">
-        <v>0.0009069023653864861</v>
+        <v>0.0007609529420733452</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.0003093210107181221</v>
+        <v>0.0003885515034198761</v>
       </c>
       <c r="GA18" t="n">
-        <v>0.0002650387468747795</v>
+        <v>2.135828253813088e-05</v>
       </c>
       <c r="GB18" t="n">
-        <v>0.0008763511432334781</v>
+        <v>0.0005219517042860389</v>
       </c>
       <c r="GC18" t="n">
-        <v>0.0001361609611194581</v>
+        <v>0.0003635637694969773</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.0006230741273611784</v>
+        <v>0.000353742012521252</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.001849808846600354</v>
+        <v>0.000316186691634357</v>
       </c>
       <c r="GF18" t="n">
-        <v>0.0007150316378101707</v>
+        <v>0.0007078646449372172</v>
       </c>
       <c r="GG18" t="n">
-        <v>0.0006383691215887666</v>
+        <v>0.0005956141976639628</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.00136775232385844</v>
+        <v>0.03508035466074944</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01777190715074539</v>
+        <v>0.1254667341709137</v>
       </c>
       <c r="C19" t="n">
-        <v>0.002357289893552661</v>
+        <v>0.01107731461524963</v>
       </c>
       <c r="D19" t="n">
-        <v>0.009700960479676723</v>
+        <v>0.1085005849599838</v>
       </c>
       <c r="E19" t="n">
-        <v>0.008108950220048428</v>
+        <v>0.02275386452674866</v>
       </c>
       <c r="F19" t="n">
-        <v>0.002982598496600986</v>
+        <v>0.06149283424019814</v>
       </c>
       <c r="G19" t="n">
-        <v>0.003247051732614636</v>
+        <v>0.04108543694019318</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0017775195883587</v>
+        <v>0.04734455049037933</v>
       </c>
       <c r="I19" t="n">
-        <v>1.322163734585047e-05</v>
+        <v>0.009104537777602673</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0009823737200349569</v>
+        <v>0.0137427719309926</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01322329510003328</v>
+        <v>0.1325716972351074</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0003793397627305239</v>
+        <v>0.02138002403080463</v>
       </c>
       <c r="M19" t="n">
-        <v>0.006902514491230249</v>
+        <v>0.1384609639644623</v>
       </c>
       <c r="N19" t="n">
-        <v>0.007116853259503841</v>
+        <v>0.05140307918190956</v>
       </c>
       <c r="O19" t="n">
-        <v>0.003595395712181926</v>
+        <v>0.05979665741324425</v>
       </c>
       <c r="P19" t="n">
-        <v>0.003359574824571609</v>
+        <v>0.02622761763632298</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.002236114116385579</v>
+        <v>0.01409537345170975</v>
       </c>
       <c r="R19" t="n">
-        <v>0.00012859285925515</v>
+        <v>0.0013883993960917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001072641462087631</v>
+        <v>0.008919191546738148</v>
       </c>
       <c r="T19" t="n">
-        <v>0.003200014121830463</v>
+        <v>0.01059613469988108</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0003980658075306565</v>
+        <v>0.007018021307885647</v>
       </c>
       <c r="V19" t="n">
-        <v>0.002550587989389896</v>
+        <v>0.009899943135678768</v>
       </c>
       <c r="W19" t="n">
-        <v>0.001835920731537044</v>
+        <v>0.02736656554043293</v>
       </c>
       <c r="X19" t="n">
-        <v>0.001870412495918572</v>
+        <v>0.02198188006877899</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.002126203384250402</v>
+        <v>0.02319205552339554</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.002673365641385317</v>
+        <v>0.02425785548985004</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.001968443859368563</v>
+        <v>0.003780634142458439</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0002452111802995205</v>
+        <v>0.002451627748087049</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.0004791761748492718</v>
+        <v>0.0005984753370285034</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.001120044849812984</v>
+        <v>0.008650990203022957</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.0007499490166082978</v>
+        <v>0.04319316148757935</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0009987115627154708</v>
+        <v>0.02924611978232861</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.0003356474335305393</v>
+        <v>0.03816202282905579</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.00125286728143692</v>
+        <v>0.008283584378659725</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.0006956075085327029</v>
+        <v>0.03814227879047394</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.0007868845132179558</v>
+        <v>0.007584564853459597</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.002167683094739914</v>
+        <v>0.00386683689430356</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.002121163299307227</v>
+        <v>0.02685081772506237</v>
       </c>
       <c r="AM19" t="n">
-        <v>4.10760949307587e-05</v>
+        <v>0.0163024514913559</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.001026191515848041</v>
+        <v>0.03351382538676262</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.001764925778843462</v>
+        <v>0.004939242266118526</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.001770356437191367</v>
+        <v>0.02060464024543762</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.001000186312012374</v>
+        <v>0.002476098015904427</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.001409822842106223</v>
+        <v>0.0002656928263604641</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.001187680754810572</v>
+        <v>0.004193442407995462</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.000535548897460103</v>
+        <v>0.01414304226636887</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.01188142318278551</v>
+        <v>0.08969027549028397</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.001197524485178292</v>
+        <v>0.02497509494423866</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.001216910197399557</v>
+        <v>0.0234706774353981</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.002513062208890915</v>
+        <v>0.07856552302837372</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.0009548445814289153</v>
+        <v>0.04087955877184868</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.0007778474246151745</v>
+        <v>0.003088314086198807</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.002199169248342514</v>
+        <v>0.02074429579079151</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.0007777392165735364</v>
+        <v>0.007514418568462133</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.0009856964461505413</v>
+        <v>0.002411446068435907</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.002563689835369587</v>
+        <v>0.03417736664414406</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.002864818787202239</v>
+        <v>0.009672984480857849</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.002754692686721683</v>
+        <v>0.02841774933040142</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.006338208448141813</v>
+        <v>0.06378601491451263</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.0001609226310392842</v>
+        <v>0.008180961012840271</v>
       </c>
       <c r="BI19" t="n">
-        <v>0.00161375047173351</v>
+        <v>0.002705621533095837</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.00237348536029458</v>
+        <v>0.04569722339510918</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.0003180751227773726</v>
+        <v>0.006382169667631388</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.002496751956641674</v>
+        <v>0.01137703098356724</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.004093441180884838</v>
+        <v>0.02153400704264641</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.001337342080660164</v>
+        <v>0.003965524956583977</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.836390144191682e-05</v>
+        <v>0.02450065314769745</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.001361729926429689</v>
+        <v>0.04100143909454346</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.001703858375549316</v>
+        <v>0.008576569147408009</v>
       </c>
       <c r="BR19" t="n">
-        <v>2.707170642679557e-05</v>
+        <v>0.009203202091157436</v>
       </c>
       <c r="BS19" t="n">
-        <v>0.0005469163879752159</v>
+        <v>0.01175722386687994</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.0003070961101911962</v>
+        <v>0.01124903652817011</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.0008713091956451535</v>
+        <v>0.001119510154239833</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.007075796835124493</v>
+        <v>0.04774516448378563</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.002957594813778996</v>
+        <v>0.01137889362871647</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.001005062833428383</v>
+        <v>0.02825546637177467</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.001216050004586577</v>
+        <v>0.01540474873036146</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.002059848979115486</v>
+        <v>0.03872973844408989</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.001927556586451828</v>
+        <v>0.02702860534191132</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.0005267897504381835</v>
+        <v>6.454112008213997e-05</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.00113053503446281</v>
+        <v>0.006281437817960978</v>
       </c>
       <c r="CD19" t="n">
-        <v>7.345130870817229e-05</v>
+        <v>0.01017819903790951</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.002665649401023984</v>
+        <v>0.03457820788025856</v>
       </c>
       <c r="CF19" t="n">
-        <v>0.0009438988636247814</v>
+        <v>0.003687758231535554</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.001276385621167719</v>
+        <v>0.03153929114341736</v>
       </c>
       <c r="CH19" t="n">
-        <v>6.750244938302785e-05</v>
+        <v>0.01112295314669609</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.001096649444662035</v>
+        <v>0.01307189464569092</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0.0005941637791693211</v>
+        <v>0.004082550760358572</v>
       </c>
       <c r="CK19" t="n">
-        <v>0.0005284324870444834</v>
+        <v>0.003750965464860201</v>
       </c>
       <c r="CL19" t="n">
-        <v>0.001241236343048513</v>
+        <v>0.003935355227440596</v>
       </c>
       <c r="CM19" t="n">
-        <v>0.00288426736369729</v>
+        <v>0.03214429691433907</v>
       </c>
       <c r="CN19" t="n">
-        <v>0.0006529551465064287</v>
+        <v>0.05145536735653877</v>
       </c>
       <c r="CO19" t="n">
-        <v>0.0009001946309581399</v>
+        <v>0.03398964554071426</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.00216955877840519</v>
+        <v>0.0299796387553215</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.00199503474868834</v>
+        <v>0.02225056290626526</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.00239738798700273</v>
+        <v>0.01319916360080242</v>
       </c>
       <c r="CS19" t="n">
-        <v>0.002868916373699903</v>
+        <v>0.0277582686394453</v>
       </c>
       <c r="CT19" t="n">
-        <v>0.002187606645748019</v>
+        <v>0.009317424148321152</v>
       </c>
       <c r="CU19" t="n">
-        <v>0.0009011310758069158</v>
+        <v>0.009899813681840897</v>
       </c>
       <c r="CV19" t="n">
-        <v>0.0002106387109961361</v>
+        <v>0.007545405998826027</v>
       </c>
       <c r="CW19" t="n">
-        <v>0.002188036683946848</v>
+        <v>0.03230270370841026</v>
       </c>
       <c r="CX19" t="n">
-        <v>0.001112921978347003</v>
+        <v>0.005506675224751234</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.001978571526706219</v>
+        <v>0.0360177755355835</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.0001876348833320662</v>
+        <v>0.0154542587697506</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.001353237661533058</v>
+        <v>0.01309962291270494</v>
       </c>
       <c r="DB19" t="n">
-        <v>0.0006693846080452204</v>
+        <v>0.005967567209154367</v>
       </c>
       <c r="DC19" t="n">
-        <v>0.0007690769270993769</v>
+        <v>0.009261365048587322</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.0006947804940864444</v>
+        <v>0.0051508704200387</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.0008304748916998506</v>
+        <v>0.02493195049464703</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.003176242578774691</v>
+        <v>0.02249144017696381</v>
       </c>
       <c r="DG19" t="n">
-        <v>0.00270383502356708</v>
+        <v>0.004282230511307716</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.007103096693754196</v>
+        <v>0.04107090458273888</v>
       </c>
       <c r="DI19" t="n">
-        <v>6.781530100852251e-05</v>
+        <v>0.01289637200534344</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.0004888697294518352</v>
+        <v>0.03059356287121773</v>
       </c>
       <c r="DK19" t="n">
-        <v>0.001874363166280091</v>
+        <v>0.01204254664480686</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.0007140344241634011</v>
+        <v>0.04034266993403435</v>
       </c>
       <c r="DM19" t="n">
-        <v>0.001279447227716446</v>
+        <v>0.01960653811693192</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.001665602903813124</v>
+        <v>0.003472633194178343</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.001213541487231851</v>
+        <v>0.02777131274342537</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.0001067010161932558</v>
+        <v>0.003486498724669218</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0.0002091791975544766</v>
+        <v>0.01718593761324883</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.0007703256560489535</v>
+        <v>0.0127218347042799</v>
       </c>
       <c r="DS19" t="n">
-        <v>1.898322807392105e-05</v>
+        <v>0.01679863221943378</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.001296766102313995</v>
+        <v>0.02761963568627834</v>
       </c>
       <c r="DU19" t="n">
-        <v>9.33269620873034e-06</v>
+        <v>0.01651712320744991</v>
       </c>
       <c r="DV19" t="n">
-        <v>0.001518283970654011</v>
+        <v>0.01781001500785351</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.0005912948399782181</v>
+        <v>0.008005407638847828</v>
       </c>
       <c r="DX19" t="n">
-        <v>0.0004297179402783513</v>
+        <v>0.01369006466120481</v>
       </c>
       <c r="DY19" t="n">
-        <v>0.002236123662441969</v>
+        <v>0.02139241062104702</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0.0005070996121503413</v>
+        <v>0.02128037065267563</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.002050388837233186</v>
+        <v>0.02827362529933453</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.0004942453233525157</v>
+        <v>0.0003317594528198242</v>
       </c>
       <c r="EC19" t="n">
-        <v>0.0006324068526737392</v>
+        <v>0.01234659366309643</v>
       </c>
       <c r="ED19" t="n">
-        <v>0.0008857071516104043</v>
+        <v>0.0495479516685009</v>
       </c>
       <c r="EE19" t="n">
-        <v>0.001065764809027314</v>
+        <v>0.02234862372279167</v>
       </c>
       <c r="EF19" t="n">
-        <v>0.001674744416959584</v>
+        <v>0.004083665087819099</v>
       </c>
       <c r="EG19" t="n">
-        <v>0.002607255009934306</v>
+        <v>0.01084204949438572</v>
       </c>
       <c r="EH19" t="n">
-        <v>0.001159347128123045</v>
+        <v>0.007383696734905243</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.0009288644650951028</v>
+        <v>0.01769532263278961</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.001523568760603666</v>
+        <v>0.01934972032904625</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.0008907742449082434</v>
+        <v>0.0106692248955369</v>
       </c>
       <c r="EL19" t="n">
-        <v>0.0009459270513616502</v>
+        <v>0.01059132255613804</v>
       </c>
       <c r="EM19" t="n">
-        <v>0.0001743385219015181</v>
+        <v>0.00551319494843483</v>
       </c>
       <c r="EN19" t="n">
-        <v>0.0005103080184198916</v>
+        <v>0.005303079728037119</v>
       </c>
       <c r="EO19" t="n">
-        <v>0.0003792230854742229</v>
+        <v>0.007575820665806532</v>
       </c>
       <c r="EP19" t="n">
-        <v>0.0002890544128604233</v>
+        <v>0.01923517696559429</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0.00188372889533639</v>
+        <v>0.004134934861212969</v>
       </c>
       <c r="ER19" t="n">
-        <v>0.001323445001617074</v>
+        <v>0.01747877709567547</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.0005076116067357361</v>
+        <v>0.02291910722851753</v>
       </c>
       <c r="ET19" t="n">
-        <v>0.001788757042959332</v>
+        <v>0.001981781795620918</v>
       </c>
       <c r="EU19" t="n">
-        <v>0.001409453107044101</v>
+        <v>0.01377121172845364</v>
       </c>
       <c r="EV19" t="n">
-        <v>0.00164878205396235</v>
+        <v>0.006928242743015289</v>
       </c>
       <c r="EW19" t="n">
-        <v>0.0005503970314748585</v>
+        <v>0.01995346136391163</v>
       </c>
       <c r="EX19" t="n">
-        <v>0.000167787482496351</v>
+        <v>0.008516046218574047</v>
       </c>
       <c r="EY19" t="n">
-        <v>0.00215203664265573</v>
+        <v>0.03758981078863144</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0.0009300001547671854</v>
+        <v>0.003384922165423632</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.001789344125427306</v>
+        <v>0.0356585904955864</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.0001891844149213284</v>
+        <v>0.006712779402732849</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.001204645377583802</v>
+        <v>0.01438729837536812</v>
       </c>
       <c r="FD19" t="n">
-        <v>0.0009726661373861134</v>
+        <v>0.0003402172587811947</v>
       </c>
       <c r="FE19" t="n">
-        <v>0.0005218154983595014</v>
+        <v>0.00962130818516016</v>
       </c>
       <c r="FF19" t="n">
-        <v>0.001359303132630885</v>
+        <v>0.001590344123542309</v>
       </c>
       <c r="FG19" t="n">
-        <v>0.001257472205907106</v>
+        <v>0.006043785251677036</v>
       </c>
       <c r="FH19" t="n">
-        <v>0.001371519407257438</v>
+        <v>0.008210564963519573</v>
       </c>
       <c r="FI19" t="n">
-        <v>0.001646693795919418</v>
+        <v>0.01311884168535471</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.002464494202286005</v>
+        <v>0.02361949905753136</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.001379867666400969</v>
+        <v>0.001605392899364233</v>
       </c>
       <c r="FL19" t="n">
-        <v>0.0010444464860484</v>
+        <v>0.0126260994002223</v>
       </c>
       <c r="FM19" t="n">
-        <v>0.001011709100566804</v>
+        <v>0.00989362969994545</v>
       </c>
       <c r="FN19" t="n">
-        <v>0.001399857457727194</v>
+        <v>0.0116993049159646</v>
       </c>
       <c r="FO19" t="n">
-        <v>0.0006227546255104244</v>
+        <v>0.02058122120797634</v>
       </c>
       <c r="FP19" t="n">
-        <v>0.0005103930598124862</v>
+        <v>0.03277895599603653</v>
       </c>
       <c r="FQ19" t="n">
-        <v>0.0004815826541744173</v>
+        <v>0.01702886447310448</v>
       </c>
       <c r="FR19" t="n">
-        <v>0.002450904808938503</v>
+        <v>0.03166619688272476</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.001238880679011345</v>
+        <v>0.001675249543040991</v>
       </c>
       <c r="FT19" t="n">
-        <v>0.001404097303748131</v>
+        <v>0.005296822171658278</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.0004738121933769435</v>
+        <v>0.003486260771751404</v>
       </c>
       <c r="FV19" t="n">
-        <v>0.0001711318036541343</v>
+        <v>0.02479140087962151</v>
       </c>
       <c r="FW19" t="n">
-        <v>0.0002879203238990158</v>
+        <v>0.01029927842319012</v>
       </c>
       <c r="FX19" t="n">
-        <v>0.001469075796194375</v>
+        <v>0.0009958620648831129</v>
       </c>
       <c r="FY19" t="n">
-        <v>0.002766100456938148</v>
+        <v>0.01199568528681993</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.001078879460692406</v>
+        <v>0.005231388844549656</v>
       </c>
       <c r="GA19" t="n">
-        <v>0.0003876433183904737</v>
+        <v>0.02624918147921562</v>
       </c>
       <c r="GB19" t="n">
-        <v>0.0009868942433968186</v>
+        <v>0.02321749180555344</v>
       </c>
       <c r="GC19" t="n">
-        <v>0.001808327622711658</v>
+        <v>0.004320456646382809</v>
       </c>
       <c r="GD19" t="n">
-        <v>0.002170912222936749</v>
+        <v>0.0355272963643074</v>
       </c>
       <c r="GE19" t="n">
-        <v>0.004825872834771872</v>
+        <v>0.04421551898121834</v>
       </c>
       <c r="GF19" t="n">
-        <v>0.001619925256818533</v>
+        <v>0.008848641067743301</v>
       </c>
       <c r="GG19" t="n">
-        <v>0.001328175771050155</v>
+        <v>0.00424814922735095</v>
       </c>
     </row>
   </sheetData>
